--- a/VENTAS INTEREY PROYECTOS Y TIENDA 2026.xlsx
+++ b/VENTAS INTEREY PROYECTOS Y TIENDA 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9cc7756de92edc38/Desktop/Zaira Palomino/PROYECTOS TERMINADOS 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{5EBE62F3-0115-4A3A-9340-47465BC04568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D27B660-7229-4EAC-9F4B-3FAC189A594B}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{5EBE62F3-0115-4A3A-9340-47465BC04568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A16C026-589C-4689-816C-484A07C1758D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,11 +20,13 @@
     <sheet name="MARZO" sheetId="9" r:id="rId5"/>
     <sheet name="ABRIL" sheetId="13" r:id="rId6"/>
     <sheet name="MAYO" sheetId="16" r:id="rId7"/>
+    <sheet name="JUNIO" sheetId="22" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">ABRIL!$A$1:$W$46</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ENERO '!$A$1:$W$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">FEBRERO!$A$1:$W$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">JUNIO!$A$1:$X$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">MARZO!$A$1:$W$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">MAYO!$A$1:$X$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VENTAS POR ASESOR'!$H$2:$N$39</definedName>
@@ -47,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1488" uniqueCount="478">
   <si>
     <t>Id</t>
   </si>
@@ -1294,9 +1296,6 @@
     <t>Utilidad despues de indirectos</t>
   </si>
   <si>
-    <t xml:space="preserve">   </t>
-  </si>
-  <si>
     <t>ALFREDO</t>
   </si>
   <si>
@@ -1337,6 +1336,153 @@
   </si>
   <si>
     <t>VENTAS TIENDA</t>
+  </si>
+  <si>
+    <t>INSTALACION ELECTRICA NUEVA BODEGA</t>
+  </si>
+  <si>
+    <t>CORGON DISEÃ‘O Y FABRICACION INDUSTRIAL</t>
+  </si>
+  <si>
+    <t>instalacion de 2 nodos de red tornos Jackeline</t>
+  </si>
+  <si>
+    <t>VENTA UPS</t>
+  </si>
+  <si>
+    <t>SERVICO DE  SHEETROCK</t>
+  </si>
+  <si>
+    <t>ALPS LOGISTICS MEXICO</t>
+  </si>
+  <si>
+    <t>VENTA DE PTZ HIKVISION (MODELO DS2A4225TID (E))</t>
+  </si>
+  <si>
+    <t>VENTA DE MATERIAL DE RED (FACEPLATE, BOBINA NETKEY CAT6, PATCHCORD 7FT, JACK CAT6)</t>
+  </si>
+  <si>
+    <t>VENTA DE TRANCEPTOR MINI-GBIC SFP+10G MULTIMODO 300M (RUJIE)</t>
+  </si>
+  <si>
+    <t>INSTALACION DE SOFTWARE AXTRAX (CONTROL DE ACCESO PLANTA 3)</t>
+  </si>
+  <si>
+    <t>($ -211.99)</t>
+  </si>
+  <si>
+    <t>INSTALACION DE 2 NODOS NUEVOS + REUBICACION DE 2 NODOS OFICINAS PLANTA 2</t>
+  </si>
+  <si>
+    <t>Renta de Escalera ElÃ©ctrica Por Mes JUNIO 2026</t>
+  </si>
+  <si>
+    <t>VENTA DE MATERIAL DE COMPUTO (MOUSE DELL)</t>
+  </si>
+  <si>
+    <t>Goods Plant:RCS #RFQReq:224297 #Vendor:262377#</t>
+  </si>
+  <si>
+    <t>VENTA DE EQUIPOS DE COMPUTO / LOGITECH C920S HD / CANAKIT RASPBERRY Pi5</t>
+  </si>
+  <si>
+    <t>#RFQReq:225413</t>
+  </si>
+  <si>
+    <t>P#13510 - PO 230310 - RevisiÃ³n y Mantto a DVR de Sistema de Circuito Cerrado de TelevisiÃ³n CCTV Planta BSN RY - PIN 6923.</t>
+  </si>
+  <si>
+    <t>P#13505 - PO 27330 - Tablet Android King Kong - Ing. Juan Sedas - Pin 8896</t>
+  </si>
+  <si>
+    <t>INSTALACION DE CHAROLA Y CANALIZACION DE RED</t>
+  </si>
+  <si>
+    <t>COTIZACION BASES PARA IDFS</t>
+  </si>
+  <si>
+    <t>SERVICIO DE MANTENIMIENTO PREVENTIVO / CORRECTIVO DE CCTV (CAMARAS INTERNAS Y EXTERNAS) _4</t>
+  </si>
+  <si>
+    <t>REUBICACION DE UNA CAMARA  DE PASSILLO HACIA ALMACEN (PLANTA 2)</t>
+  </si>
+  <si>
+    <t>($ -840.60)</t>
+  </si>
+  <si>
+    <t>(-7.34 %)</t>
+  </si>
+  <si>
+    <t>STANDARD MOTOR PRODUCTS DE MEXICO</t>
+  </si>
+  <si>
+    <t>REUBICACION DE ALMACEN (PUENTES)</t>
+  </si>
+  <si>
+    <t>Material de red cotizaciÃ³n por favor gracias</t>
+  </si>
+  <si>
+    <t>P#13445 - PO 480R7496- Bobina cable UTP, Conectores RJ45, Jack RJ45 - Pin 2833.</t>
+  </si>
+  <si>
+    <t>BIOSERVICIOS INTEGRALES DEL NORESTE</t>
+  </si>
+  <si>
+    <t>REPARACION DE CONTROL DE ACCESO ALBERTO MORA</t>
+  </si>
+  <si>
+    <t>KOHLER REYNOSA</t>
+  </si>
+  <si>
+    <t>P#13436 - PO 4201205825 - RFQ 934 TV SAMSUNG 50" - Pin 6705.</t>
+  </si>
+  <si>
+    <t>Goods Plant:RAM #RFQReq:221137 #Vendor:257420#</t>
+  </si>
+  <si>
+    <t>P#13395 - PO PO 480R7471 Cotizacion chapa de seguridad - Daniel Guillermo _ Pin 1623</t>
+  </si>
+  <si>
+    <t>Bajadas Red Cel 21</t>
+  </si>
+  <si>
+    <t>REQ - 1187 - ADAPTADOR HEMBRA MACHO</t>
+  </si>
+  <si>
+    <t>SUMINISTRO E INSTALACION DE 24 NODOS DE RED (AREA NUEVA PRODUCCION) NUHEAT</t>
+  </si>
+  <si>
+    <t>COTIZAR CABLE DE INTERNET PARA CAMARAS DE INSPECCION</t>
+  </si>
+  <si>
+    <t>CotizaciÃ³n DC 12V 3A Power Adapter</t>
+  </si>
+  <si>
+    <t>PV#13211 - OC #27150 - Jacks - Patch Cords - Pin 1866</t>
+  </si>
+  <si>
+    <t>#13166 - PO # 4502008841 - Rfq 2873713 - KARINA GAMBOA - ENRIQUE CERVANTES - PLANTA RAM - PIN 1121.</t>
+  </si>
+  <si>
+    <t>#13165 - PO # 4502008847 - Rfq 2873720 - KARINA GAMBOA - ANDREA GALLEGOS - PLANTA RAM - PIN 1121.</t>
+  </si>
+  <si>
+    <t>#13164 - PO # 4502008843 - Rfq 2873715 - KARINA GAMBOA - MATEO SEQUERA - PLANTA RAM - PIN 2357.</t>
+  </si>
+  <si>
+    <t>#13163 - PO # 4502008614 Rfq 2873710 - KARINA GAMBOA - MATEO SEQUERA - PLANTA RAM - PIN 7053.</t>
+  </si>
+  <si>
+    <t>COTIZACION Lector de huella digital USB</t>
+  </si>
+  <si>
+    <t>Cotizacion IDF</t>
+  </si>
+  <si>
+    <t>SUPPLY AND INSTALLATION OF RADIUS NETWORK NODES, USER NETWORK, CAMARAS NODES AND ELECTRICAL DOWNLINES (ELECTRIC TRANSFORMER INCLUDED (PLANTA 3) CAMARAS_COTIZACION EN PESOS</t>
+  </si>
+  <si>
+    <t>MATERIAL REAL PESOS</t>
   </si>
 </sst>
 </file>
@@ -1354,11 +1500,18 @@
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1553,7 +1706,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1641,6 +1794,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA3EAFB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1839,34 +1998,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="9">
+  <cellStyleXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="206">
+  <cellXfs count="217">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1880,79 +2040,79 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -1961,348 +2121,365 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="15" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="17" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="18" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5"/>
-    <xf numFmtId="14" fontId="8" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="8" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="4" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="15" fillId="7" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="0" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="16" fillId="7" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="17" fillId="8" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" xfId="6" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="8" borderId="4" xfId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="7" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="7" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="7" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="7" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="21" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="22" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="13" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="14" fillId="7" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="13" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="7" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="19" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="23" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="24" fillId="12" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="4" xfId="7" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="15" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="8" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="8" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="8" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="8" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="5" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="8" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="8" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="4" xfId="8" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="8" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="8" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="5" fillId="0" borderId="0" xfId="5" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="12" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="8" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="9" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="0" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="10" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="14" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="25" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="14" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="25" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="25" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="9"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="0" xfId="9" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="9" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="1" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="4" xfId="9" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="15" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="4" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="13" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="24" fillId="0" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="19" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="9">
+  <cellStyles count="10">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="3" xr:uid="{8636CDB4-E18C-4D42-87E5-89123EFD6A79}"/>
@@ -2311,6 +2488,7 @@
     <cellStyle name="Normal 4" xfId="6" xr:uid="{16746046-88A9-4A61-87D1-0C8F12EDEDDA}"/>
     <cellStyle name="Normal 5" xfId="7" xr:uid="{BFC8F650-34D6-40F5-BB3F-926D5B8AC3D7}"/>
     <cellStyle name="Normal 6" xfId="8" xr:uid="{70098147-3CB6-4069-A3DB-97ABEE09C550}"/>
+    <cellStyle name="Normal 7" xfId="9" xr:uid="{4D69DB7E-714D-46EC-9BFD-284C9B6BCCCF}"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="12">
@@ -2812,7 +2990,9 @@
       <c r="F2" s="21">
         <v>3877.12</v>
       </c>
-      <c r="G2" s="19"/>
+      <c r="G2" s="21">
+        <v>1017556.972624</v>
+      </c>
       <c r="H2" s="19"/>
       <c r="I2" s="19"/>
       <c r="J2" s="19"/>
@@ -2821,7 +3001,7 @@
       <c r="M2" s="19"/>
       <c r="N2" s="50">
         <f t="shared" ref="N2:N7" si="0">SUM(B2:M2)</f>
-        <v>4981781.9899999993</v>
+        <v>5999338.9626239995</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2843,7 +3023,9 @@
       <c r="F3" s="21">
         <v>42531.61</v>
       </c>
-      <c r="G3" s="19"/>
+      <c r="G3" s="21">
+        <v>583579.35000000009</v>
+      </c>
       <c r="H3" s="19"/>
       <c r="I3" s="19"/>
       <c r="J3" s="19"/>
@@ -2852,7 +3034,7 @@
       <c r="M3" s="19"/>
       <c r="N3" s="50">
         <f t="shared" si="0"/>
-        <v>2754510.5415920005</v>
+        <v>3338089.8915920006</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2874,7 +3056,9 @@
       <c r="F4" s="21">
         <v>51126.195238</v>
       </c>
-      <c r="G4" s="19"/>
+      <c r="G4" s="21">
+        <v>109584.052624</v>
+      </c>
       <c r="H4" s="19"/>
       <c r="I4" s="19"/>
       <c r="J4" s="19"/>
@@ -2883,7 +3067,7 @@
       <c r="M4" s="19"/>
       <c r="N4" s="50">
         <f t="shared" si="0"/>
-        <v>1412225.405338</v>
+        <v>1521809.457962</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2905,7 +3089,9 @@
       <c r="F5" s="21">
         <v>253025.72000000003</v>
       </c>
-      <c r="G5" s="19"/>
+      <c r="G5" s="21">
+        <v>2245236.12</v>
+      </c>
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
       <c r="J5" s="19"/>
@@ -2914,7 +3100,7 @@
       <c r="M5" s="19"/>
       <c r="N5" s="50">
         <f t="shared" si="0"/>
-        <v>1482857.1900000002</v>
+        <v>3728093.3100000005</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2936,7 +3122,9 @@
       <c r="F6" s="21">
         <v>103280.53</v>
       </c>
-      <c r="G6" s="19"/>
+      <c r="G6" s="21">
+        <v>28503.7</v>
+      </c>
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
       <c r="J6" s="19"/>
@@ -2945,7 +3133,7 @@
       <c r="M6" s="19"/>
       <c r="N6" s="50">
         <f t="shared" si="0"/>
-        <v>404310.59700000007</v>
+        <v>432814.29700000008</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2967,7 +3155,9 @@
       <c r="F7" s="21">
         <v>5832.61</v>
       </c>
-      <c r="G7" s="19"/>
+      <c r="G7" s="21">
+        <v>44177.47</v>
+      </c>
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
       <c r="J7" s="19"/>
@@ -2976,7 +3166,7 @@
       <c r="M7" s="19"/>
       <c r="N7" s="50">
         <f t="shared" si="0"/>
-        <v>38366.17</v>
+        <v>82543.64</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -3003,7 +3193,7 @@
       </c>
       <c r="G8" s="20">
         <f t="shared" ref="G8:L8" si="1">SUM(G2:G7)</f>
-        <v>0</v>
+        <v>4028637.6652480005</v>
       </c>
       <c r="H8" s="20">
         <f t="shared" si="1"/>
@@ -3031,7 +3221,7 @@
       </c>
       <c r="N8" s="20">
         <f>SUM(N2:N7)</f>
-        <v>11074051.893930001</v>
+        <v>15102689.559178002</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -3097,7 +3287,9 @@
       <c r="F10" s="21">
         <v>193901.46</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="21">
+        <v>311296.53999999998</v>
+      </c>
       <c r="H10" s="21"/>
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
@@ -3106,7 +3298,7 @@
       <c r="M10" s="21"/>
       <c r="N10" s="52">
         <f>SUM(B10:M10)</f>
-        <v>1646736.75</v>
+        <v>1958033.29</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -3135,7 +3327,7 @@
       </c>
       <c r="G11" s="114">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4339934.2052480001</v>
       </c>
       <c r="H11" s="114">
         <f t="shared" si="2"/>
@@ -3163,7 +3355,7 @@
       </c>
       <c r="N11" s="114">
         <f t="shared" si="2"/>
-        <v>12720788.643930001</v>
+        <v>17060722.849178001</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -3185,44 +3377,44 @@
       <c r="N13" s="53"/>
     </row>
     <row r="14" spans="1:14" ht="31.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="198" t="s">
+      <c r="A14" s="196" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="192" t="s">
+      <c r="B14" s="190" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="189" t="s">
+        <v>370</v>
+      </c>
+      <c r="D14" s="190" t="s">
+        <v>420</v>
+      </c>
+      <c r="E14" s="190" t="s">
+        <v>419</v>
+      </c>
+      <c r="F14" s="191" t="s">
+        <v>421</v>
+      </c>
+      <c r="G14" s="192" t="s">
         <v>428</v>
       </c>
-      <c r="C14" s="191" t="s">
-        <v>370</v>
-      </c>
-      <c r="D14" s="192" t="s">
-        <v>421</v>
-      </c>
-      <c r="E14" s="192" t="s">
-        <v>420</v>
-      </c>
-      <c r="F14" s="193" t="s">
+      <c r="H14" s="193" t="s">
         <v>422</v>
       </c>
-      <c r="G14" s="194" t="s">
-        <v>429</v>
-      </c>
-      <c r="H14" s="195" t="s">
+      <c r="I14" s="193" t="s">
+        <v>424</v>
+      </c>
+      <c r="J14" s="193" t="s">
+        <v>425</v>
+      </c>
+      <c r="K14" s="198" t="s">
+        <v>227</v>
+      </c>
+      <c r="L14" s="198" t="s">
         <v>423</v>
       </c>
-      <c r="I14" s="195" t="s">
-        <v>425</v>
-      </c>
-      <c r="J14" s="195" t="s">
+      <c r="M14" s="198" t="s">
         <v>426</v>
-      </c>
-      <c r="K14" s="200" t="s">
-        <v>227</v>
-      </c>
-      <c r="L14" s="200" t="s">
-        <v>424</v>
-      </c>
-      <c r="M14" s="200" t="s">
-        <v>427</v>
       </c>
       <c r="N14" s="53"/>
     </row>
@@ -3246,7 +3438,7 @@
         <v>1561964.6800000002</v>
       </c>
       <c r="F15" s="29">
-        <f>+D15-E15</f>
+        <f t="shared" ref="F15:F26" si="3">+D15-E15</f>
         <v>338297.21671199938</v>
       </c>
       <c r="G15" s="29">
@@ -3264,11 +3456,11 @@
         <v>-21319.489999999991</v>
       </c>
       <c r="K15" s="29">
-        <f>+B15+G15</f>
+        <f t="shared" ref="K15:K26" si="4">+B15+G15</f>
         <v>3535254.6215999997</v>
       </c>
       <c r="L15" s="29">
-        <f>+D15+H15</f>
+        <f t="shared" ref="L15:L26" si="5">+D15+H15</f>
         <v>1977028.0567119995</v>
       </c>
       <c r="M15" s="29">
@@ -3289,7 +3481,7 @@
         <v>1113152.6227819999</v>
       </c>
       <c r="D16" s="29">
-        <f t="shared" ref="D16:D26" si="3">+B16-C16</f>
+        <f t="shared" ref="D16:D26" si="6">+B16-C16</f>
         <v>1326239.7338179997</v>
       </c>
       <c r="E16" s="182">
@@ -3297,7 +3489,7 @@
         <v>1155469.9100000001</v>
       </c>
       <c r="F16" s="29">
-        <f>+D16-E16</f>
+        <f t="shared" si="3"/>
         <v>170769.82381799957</v>
       </c>
       <c r="G16" s="29">
@@ -3311,19 +3503,19 @@
         <v>104434.14000000001</v>
       </c>
       <c r="J16" s="29">
-        <f t="shared" ref="J16:J26" si="4">+H16-I16</f>
+        <f t="shared" ref="J16:J26" si="7">+H16-I16</f>
         <v>-25562.650000000009</v>
       </c>
       <c r="K16" s="29">
-        <f>+B16+G16</f>
+        <f t="shared" si="4"/>
         <v>2870956.3065999998</v>
       </c>
       <c r="L16" s="29">
-        <f>+D16+H16</f>
+        <f t="shared" si="5"/>
         <v>1405111.2238179997</v>
       </c>
       <c r="M16" s="29">
-        <f t="shared" ref="M16:M26" si="5">+F16+J16</f>
+        <f t="shared" ref="M16:M26" si="8">+F16+J16</f>
         <v>145207.17381799954</v>
       </c>
       <c r="N16" s="53"/>
@@ -3340,7 +3532,7 @@
         <v>1608971.6615169998</v>
       </c>
       <c r="D17" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1657307.6444830005</v>
       </c>
       <c r="E17" s="16">
@@ -3348,7 +3540,7 @@
         <v>1263999.6400000001</v>
       </c>
       <c r="F17" s="29">
-        <f>+D17-E17</f>
+        <f t="shared" si="3"/>
         <v>393308.00448300038</v>
       </c>
       <c r="G17" s="29">
@@ -3362,19 +3554,19 @@
         <v>86532.88</v>
       </c>
       <c r="J17" s="29">
+        <f t="shared" si="7"/>
+        <v>-13704.64</v>
+      </c>
+      <c r="K17" s="29">
         <f t="shared" si="4"/>
-        <v>-13704.64</v>
-      </c>
-      <c r="K17" s="29">
-        <f>+B17+G17</f>
         <v>3674351.4560000002</v>
       </c>
       <c r="L17" s="29">
-        <f>+D17+H17</f>
+        <f t="shared" si="5"/>
         <v>1730135.8844830005</v>
       </c>
       <c r="M17" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>379603.36448300036</v>
       </c>
       <c r="N17" s="53"/>
@@ -3391,7 +3583,7 @@
         <v>788704.19898799993</v>
       </c>
       <c r="D18" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>1003459.3755040001</v>
       </c>
       <c r="E18" s="16">
@@ -3399,7 +3591,7 @@
         <v>1144755.21</v>
       </c>
       <c r="F18" s="29">
-        <f>+D18-E18</f>
+        <f t="shared" si="3"/>
         <v>-141295.83449599985</v>
       </c>
       <c r="G18" s="29">
@@ -3413,19 +3605,19 @@
         <v>74375.320000000007</v>
       </c>
       <c r="J18" s="29">
+        <f t="shared" si="7"/>
+        <v>-36884.400000000009</v>
+      </c>
+      <c r="K18" s="29">
         <f t="shared" si="4"/>
-        <v>-36884.400000000009</v>
-      </c>
-      <c r="K18" s="29">
-        <f>+B18+G18</f>
         <v>1986651.014492</v>
       </c>
       <c r="L18" s="29">
-        <f>+D18+H18</f>
+        <f t="shared" si="5"/>
         <v>1040950.2955040002</v>
       </c>
-      <c r="M18" s="29">
-        <f t="shared" si="5"/>
+      <c r="M18" s="216">
+        <f t="shared" si="8"/>
         <v>-178180.23449599987</v>
       </c>
       <c r="N18" s="53"/>
@@ -3442,7 +3634,7 @@
         <v>291171.06359999999</v>
       </c>
       <c r="D19" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>168502.72163799999</v>
       </c>
       <c r="E19" s="183">
@@ -3450,7 +3642,7 @@
         <v>1199324.44</v>
       </c>
       <c r="F19" s="29">
-        <f>+D19-E19</f>
+        <f t="shared" si="3"/>
         <v>-1030821.718362</v>
       </c>
       <c r="G19" s="29">
@@ -3463,19 +3655,19 @@
         <v>66678.87</v>
       </c>
       <c r="J19" s="29">
+        <f t="shared" si="7"/>
+        <v>-26790.929999999993</v>
+      </c>
+      <c r="K19" s="29">
         <f t="shared" si="4"/>
-        <v>-26790.929999999993</v>
-      </c>
-      <c r="K19" s="29">
-        <f>+B19+G19</f>
         <v>653575.24523799994</v>
       </c>
       <c r="L19" s="29">
-        <f>+D19+H19</f>
+        <f t="shared" si="5"/>
         <v>208390.66163799999</v>
       </c>
-      <c r="M19" s="29">
-        <f t="shared" si="5"/>
+      <c r="M19" s="216">
+        <f t="shared" si="8"/>
         <v>-1057612.648362</v>
       </c>
       <c r="N19" s="53"/>
@@ -3484,35 +3676,49 @@
       <c r="A20" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
+      <c r="B20" s="29">
+        <f>+G8</f>
+        <v>4028637.6652480005</v>
+      </c>
+      <c r="C20" s="29">
+        <v>2023683.6897479999</v>
+      </c>
       <c r="D20" s="29">
+        <f t="shared" si="6"/>
+        <v>2004953.9755000006</v>
+      </c>
+      <c r="E20" s="16">
+        <f>1305267.63-42961.88</f>
+        <v>1262305.75</v>
+      </c>
+      <c r="F20" s="29">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="29">
-        <f>+D20-E20</f>
-        <v>0</v>
-      </c>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="29"/>
+        <v>742648.22550000064</v>
+      </c>
+      <c r="G20" s="16">
+        <v>311296.53999999998</v>
+      </c>
+      <c r="H20" s="16">
+        <v>55365.91</v>
+      </c>
+      <c r="I20" s="29">
+        <v>42961.880000000005</v>
+      </c>
       <c r="J20" s="29">
+        <f t="shared" si="7"/>
+        <v>12404.029999999999</v>
+      </c>
+      <c r="K20" s="29">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="29">
-        <f>+B20+G20</f>
-        <v>0</v>
+        <v>4339934.2052480001</v>
       </c>
       <c r="L20" s="29">
-        <f>+D20+H20</f>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2060319.8855000006</v>
       </c>
       <c r="M20" s="29">
-        <f t="shared" si="5"/>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>755052.25550000067</v>
       </c>
       <c r="N20" s="53"/>
     </row>
@@ -3523,31 +3729,31 @@
       <c r="B21" s="15"/>
       <c r="C21" s="15"/>
       <c r="D21" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="29">
-        <f>+D21-E21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G21" s="15"/>
       <c r="H21" s="15"/>
       <c r="I21" s="29"/>
       <c r="J21" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K21" s="29">
-        <f>+B21+G21</f>
-        <v>0</v>
-      </c>
       <c r="L21" s="29">
-        <f>+D21+H21</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M21" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N21" s="53"/>
@@ -3559,31 +3765,31 @@
       <c r="B22" s="15"/>
       <c r="C22" s="15"/>
       <c r="D22" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="29">
-        <f>+D22-E22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G22" s="15"/>
       <c r="H22" s="15"/>
       <c r="I22" s="29"/>
       <c r="J22" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K22" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K22" s="29">
-        <f>+B22+G22</f>
-        <v>0</v>
-      </c>
       <c r="L22" s="29">
-        <f>+D22+H22</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M22" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N22" s="53"/>
@@ -3595,31 +3801,31 @@
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
       <c r="D23" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="29">
-        <f>+D23-E23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G23" s="15"/>
       <c r="H23" s="15"/>
       <c r="I23" s="29"/>
       <c r="J23" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K23" s="29">
-        <f>+B23+G23</f>
-        <v>0</v>
-      </c>
       <c r="L23" s="29">
-        <f>+D23+H23</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M23" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N23" s="53"/>
@@ -3631,31 +3837,31 @@
       <c r="B24" s="15"/>
       <c r="C24" s="15"/>
       <c r="D24" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="29">
-        <f>+D24-E24</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="15"/>
       <c r="I24" s="29"/>
       <c r="J24" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K24" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K24" s="29">
-        <f>+B24+G24</f>
-        <v>0</v>
-      </c>
       <c r="L24" s="29">
-        <f>+D24+H24</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M24" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N24" s="53"/>
@@ -3667,31 +3873,31 @@
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
       <c r="D25" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E25" s="15"/>
       <c r="F25" s="29">
-        <f>+D25-E25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G25" s="15"/>
       <c r="H25" s="15"/>
       <c r="I25" s="29"/>
       <c r="J25" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K25" s="29">
-        <f>+B25+G25</f>
-        <v>0</v>
-      </c>
       <c r="L25" s="29">
-        <f>+D25+H25</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M25" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N25" s="53"/>
@@ -3703,86 +3909,86 @@
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="29">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E26" s="15"/>
       <c r="F26" s="29">
-        <f>+D26-E26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G26" s="15"/>
       <c r="H26" s="15"/>
       <c r="I26" s="29"/>
       <c r="J26" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="K26" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K26" s="29">
-        <f>+B26+G26</f>
-        <v>0</v>
-      </c>
       <c r="L26" s="29">
-        <f>+D26+H26</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M26" s="29">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="N26" s="53"/>
     </row>
     <row r="27" spans="1:14" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="197" t="s">
+      <c r="A27" s="195" t="s">
         <v>225</v>
       </c>
-      <c r="B27" s="196">
+      <c r="B27" s="194">
         <f>SUM(B15:B26)</f>
-        <v>11074051.893929999</v>
-      </c>
-      <c r="C27" s="196">
-        <f t="shared" ref="C27" si="6">SUM(C15:C26)</f>
-        <v>5018280.5217749998</v>
-      </c>
-      <c r="D27" s="196">
+        <v>15102689.559178</v>
+      </c>
+      <c r="C27" s="194">
+        <f t="shared" ref="C27" si="9">SUM(C15:C26)</f>
+        <v>7041964.2115230002</v>
+      </c>
+      <c r="D27" s="194">
         <f>SUM(D15:D26)</f>
-        <v>6055771.3721549995</v>
-      </c>
-      <c r="E27" s="196">
+        <v>8060725.3476550002</v>
+      </c>
+      <c r="E27" s="194">
         <f>SUM(E15:E26)</f>
-        <v>6325513.8800000008</v>
-      </c>
-      <c r="F27" s="199">
+        <v>7587819.6300000008</v>
+      </c>
+      <c r="F27" s="197">
         <f>SUM(F15:F26)</f>
-        <v>-269742.50784500048</v>
-      </c>
-      <c r="G27" s="196">
+        <v>472905.71765500016</v>
+      </c>
+      <c r="G27" s="194">
         <f>SUM(G15:G26)</f>
-        <v>1646736.75</v>
-      </c>
-      <c r="H27" s="196">
+        <v>1958033.29</v>
+      </c>
+      <c r="H27" s="194">
         <f>SUM(H15:H26)</f>
-        <v>305844.75</v>
-      </c>
-      <c r="I27" s="196">
-        <f t="shared" ref="I27:J27" si="7">SUM(I15:I26)</f>
-        <v>430106.86000000004</v>
-      </c>
-      <c r="J27" s="196">
-        <f t="shared" si="7"/>
-        <v>-124262.11</v>
-      </c>
-      <c r="K27" s="201">
+        <v>361210.66000000003</v>
+      </c>
+      <c r="I27" s="194">
+        <f t="shared" ref="I27:J27" si="10">SUM(I15:I26)</f>
+        <v>473068.74000000005</v>
+      </c>
+      <c r="J27" s="194">
+        <f t="shared" si="10"/>
+        <v>-111858.08</v>
+      </c>
+      <c r="K27" s="199">
         <f>SUM(K15:K26)</f>
-        <v>12720788.643929999</v>
-      </c>
-      <c r="L27" s="201">
+        <v>17060722.849178001</v>
+      </c>
+      <c r="L27" s="199">
         <f>SUM(L15:L26)</f>
-        <v>6361616.1221549995</v>
-      </c>
-      <c r="M27" s="201">
+        <v>8421936.0076550003</v>
+      </c>
+      <c r="M27" s="199">
         <f>SUM(M15:M26)</f>
-        <v>-394004.61784500058</v>
+        <v>361047.63765500009</v>
       </c>
       <c r="N27" s="53"/>
     </row>
@@ -3791,41 +3997,41 @@
       <c r="B28" s="29"/>
       <c r="C28" s="45">
         <f>+C27/B27</f>
-        <v>0.45315667380298813</v>
+        <v>0.46627219502393558</v>
       </c>
       <c r="D28" s="45">
         <f>+D27/B27</f>
-        <v>0.54684332619701181</v>
+        <v>0.53372780497606442</v>
       </c>
       <c r="E28" s="153">
         <f>+E27/B27</f>
-        <v>0.57120139408658488</v>
-      </c>
-      <c r="F28" s="204">
+        <v>0.50241512283412026</v>
+      </c>
+      <c r="F28" s="200">
         <f>+F27/B27</f>
-        <v>-2.4358067889572919E-2</v>
+        <v>3.1312682141944208E-2</v>
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="153">
         <f>+H27/G27</f>
-        <v>0.18572777342826655</v>
+        <v>0.18447626087092728</v>
       </c>
       <c r="I28" s="153">
         <f>+I27/G27</f>
-        <v>0.2611873816504065</v>
-      </c>
-      <c r="J28" s="205">
+        <v>0.24160403319802598</v>
+      </c>
+      <c r="J28" s="201">
         <f>+J27/G27</f>
-        <v>-7.5459608222139943E-2</v>
+        <v>-5.7127772327098689E-2</v>
       </c>
       <c r="K28" s="45"/>
       <c r="L28" s="45">
         <f>+L27/K27</f>
-        <v>0.50009604751908077</v>
-      </c>
-      <c r="M28" s="205">
+        <v>0.49364473487480487</v>
+      </c>
+      <c r="M28" s="201">
         <f>+M27/K27</f>
-        <v>-3.0973285452156964E-2</v>
+        <v>2.1162505296333071E-2</v>
       </c>
       <c r="N28" s="53"/>
     </row>
@@ -3852,7 +4058,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.44140625" customWidth="1"/>
@@ -3911,8 +4117,8 @@
     </row>
     <row r="3" spans="1:14" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="139"/>
-      <c r="B3" s="189"/>
-      <c r="C3" s="190"/>
+      <c r="B3" s="204"/>
+      <c r="C3" s="205"/>
       <c r="D3" s="139"/>
       <c r="F3" s="55"/>
       <c r="G3" s="55"/>
@@ -4807,7 +5013,7 @@
       <c r="F28" s="131"/>
       <c r="G28" s="97"/>
       <c r="H28" s="71" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I28" s="13"/>
       <c r="J28" s="26"/>
@@ -5441,21 +5647,181 @@
       <c r="G52" s="121"/>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D54" s="118">
-        <f>+D52+D41+D30+D20+D10</f>
-        <v>11074051.893929999</v>
+      <c r="A54" s="122">
+        <v>46174</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D55" s="118">
-        <f>11074059-D54</f>
-        <v>7.1060700006783009</v>
+      <c r="A55" s="125" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="126">
+        <v>17.392199999999999</v>
+      </c>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="55"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B56" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="E56" s="54" t="s">
+        <v>294</v>
+      </c>
+      <c r="F56" s="75" t="s">
+        <v>299</v>
+      </c>
+      <c r="G56" s="75" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D57" s="10" t="s">
-        <v>415</v>
-      </c>
+      <c r="A57" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" s="26">
+        <v>62433.85</v>
+      </c>
+      <c r="C57" s="26">
+        <v>6662.38</v>
+      </c>
+      <c r="D57" s="127">
+        <f>+B57+JUNIO!J45</f>
+        <v>4159867.2641200009</v>
+      </c>
+      <c r="E57" s="97">
+        <f>+D57-$E$2</f>
+        <v>3389867.2641200009</v>
+      </c>
+      <c r="F57" s="131"/>
+      <c r="G57" s="97"/>
+    </row>
+    <row r="58" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" s="26">
+        <v>583579.35000000009</v>
+      </c>
+      <c r="C58" s="26"/>
+      <c r="D58" s="127">
+        <f t="shared" ref="D58:D62" si="11">+B58+C58*$B$33</f>
+        <v>583579.35000000009</v>
+      </c>
+      <c r="E58" s="97">
+        <f t="shared" ref="E58:E62" si="12">+D58-$E$2</f>
+        <v>-186420.64999999991</v>
+      </c>
+      <c r="F58" s="131"/>
+      <c r="G58" s="97"/>
+    </row>
+    <row r="59" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="B59" s="26">
+        <v>2245236.12</v>
+      </c>
+      <c r="C59" s="26"/>
+      <c r="D59" s="127">
+        <f t="shared" si="11"/>
+        <v>2245236.12</v>
+      </c>
+      <c r="E59" s="97">
+        <f t="shared" si="12"/>
+        <v>1475236.12</v>
+      </c>
+      <c r="F59" s="131"/>
+      <c r="G59" s="97"/>
+    </row>
+    <row r="60" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="26">
+        <v>28503.7</v>
+      </c>
+      <c r="C60" s="26"/>
+      <c r="D60" s="127">
+        <f t="shared" si="11"/>
+        <v>28503.7</v>
+      </c>
+      <c r="E60" s="97">
+        <f t="shared" si="12"/>
+        <v>-741496.3</v>
+      </c>
+      <c r="F60" s="131"/>
+      <c r="G60" s="97"/>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="26">
+        <v>970406.77</v>
+      </c>
+      <c r="C61" s="26">
+        <v>2726.58</v>
+      </c>
+      <c r="D61" s="127">
+        <f>+B61+JUNIO!J28</f>
+        <v>1017556.972624</v>
+      </c>
+      <c r="E61" s="97">
+        <f t="shared" si="12"/>
+        <v>247556.97262400005</v>
+      </c>
+      <c r="F61" s="132"/>
+      <c r="G61" s="98"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>316</v>
+      </c>
+      <c r="B62" s="26">
+        <v>44177.47</v>
+      </c>
+      <c r="C62" s="26"/>
+      <c r="D62" s="127">
+        <f t="shared" si="11"/>
+        <v>44177.47</v>
+      </c>
+      <c r="E62" s="97">
+        <f t="shared" si="12"/>
+        <v>-725822.53</v>
+      </c>
+      <c r="F62" s="133"/>
+      <c r="G62" s="13"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="123" t="s">
+        <v>366</v>
+      </c>
+      <c r="B63" s="124">
+        <f>SUM(B57:B62)</f>
+        <v>3934337.2600000007</v>
+      </c>
+      <c r="C63" s="124">
+        <f>SUM(C57:C62)</f>
+        <v>9388.9599999999991</v>
+      </c>
+      <c r="D63" s="128">
+        <f>SUM(D57:D62)</f>
+        <v>8078920.8767440012</v>
+      </c>
+      <c r="E63" s="121"/>
+      <c r="F63" s="134"/>
+      <c r="G63" s="121"/>
     </row>
   </sheetData>
   <autoFilter ref="H2:N39" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
@@ -11115,7 +11481,7 @@
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="H40" s="172" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I40" s="171">
         <v>19259.603900000002</v>
@@ -11139,7 +11505,7 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="H41" s="172" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I41" s="173">
         <v>752666.71270000003</v>
@@ -14262,7 +14628,7 @@
     </row>
     <row r="43" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="H43" s="62" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I43" s="174">
         <v>127463.59460000001</v>
@@ -14274,7 +14640,7 @@
     </row>
     <row r="44" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="H44" s="62" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I44" s="174">
         <v>682206.85440000007</v>
@@ -14294,7 +14660,7 @@
     </row>
     <row r="45" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="H45" s="62" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="I45" s="174">
         <v>15334.527000000002</v>
@@ -17706,7 +18072,7 @@
         <v>1.429751111111111</v>
       </c>
       <c r="H47" s="173" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I47" s="177">
         <v>87051.894491999992</v>
@@ -17960,7 +18326,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F4EBE57-6C17-4D87-B36A-3DB604C88F7B}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
@@ -18049,7 +18414,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="160">
         <v>13462</v>
       </c>
@@ -18125,7 +18490,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="160">
         <v>13454</v>
       </c>
@@ -18154,7 +18519,7 @@
         <v>8670.4699999999993</v>
       </c>
       <c r="J3" s="167">
-        <f t="shared" ref="J3:J27" si="0">+I3*H3</f>
+        <f>+I3*H3</f>
         <v>8670.4699999999993</v>
       </c>
       <c r="K3" s="167">
@@ -18170,7 +18535,7 @@
         <v>2661.94</v>
       </c>
       <c r="O3" s="167">
-        <f t="shared" ref="O3:O28" si="1">+H3*N3</f>
+        <f t="shared" ref="O3:O28" si="0">+H3*N3</f>
         <v>2661.94</v>
       </c>
       <c r="P3" s="167">
@@ -18201,7 +18566,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="160">
         <v>13441</v>
       </c>
@@ -18230,7 +18595,7 @@
         <v>4002</v>
       </c>
       <c r="J4" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="J3:J27" si="1">+I4*H4</f>
         <v>4002</v>
       </c>
       <c r="K4" s="167">
@@ -18246,7 +18611,7 @@
         <v>2629.12</v>
       </c>
       <c r="O4" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2629.12</v>
       </c>
       <c r="P4" s="167">
@@ -18277,7 +18642,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="160">
         <v>13432</v>
       </c>
@@ -18306,25 +18671,25 @@
         <v>74764.800000000003</v>
       </c>
       <c r="J5" s="167">
+        <f t="shared" si="1"/>
+        <v>74764.800000000003</v>
+      </c>
+      <c r="K5" s="167">
+        <v>10218.64</v>
+      </c>
+      <c r="L5" s="167">
+        <v>12212.36</v>
+      </c>
+      <c r="M5" s="167">
+        <v>0</v>
+      </c>
+      <c r="N5" s="167">
+        <v>74764.800000000003</v>
+      </c>
+      <c r="O5" s="167">
         <f t="shared" si="0"/>
         <v>74764.800000000003</v>
       </c>
-      <c r="K5" s="167">
-        <v>10218.64</v>
-      </c>
-      <c r="L5" s="167">
-        <v>12212.36</v>
-      </c>
-      <c r="M5" s="167">
-        <v>0</v>
-      </c>
-      <c r="N5" s="167">
-        <v>74764.800000000003</v>
-      </c>
-      <c r="O5" s="167">
-        <f t="shared" si="1"/>
-        <v>74764.800000000003</v>
-      </c>
       <c r="P5" s="167">
         <v>0</v>
       </c>
@@ -18353,7 +18718,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="160">
         <v>13410</v>
       </c>
@@ -18382,7 +18747,7 @@
         <v>12760.02</v>
       </c>
       <c r="J6" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>12760.02</v>
       </c>
       <c r="K6" s="167">
@@ -18398,7 +18763,7 @@
         <v>7350</v>
       </c>
       <c r="O6" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7350</v>
       </c>
       <c r="P6" s="167">
@@ -18429,7 +18794,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="160">
         <v>13387</v>
       </c>
@@ -18458,7 +18823,7 @@
         <v>131414.39999999999</v>
       </c>
       <c r="J7" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>131414.39999999999</v>
       </c>
       <c r="K7" s="167">
@@ -18474,7 +18839,7 @@
         <v>90050</v>
       </c>
       <c r="O7" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>90050</v>
       </c>
       <c r="P7" s="167">
@@ -18505,7 +18870,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="160">
         <v>13386</v>
       </c>
@@ -18534,25 +18899,25 @@
         <v>10939.5</v>
       </c>
       <c r="J8" s="167">
+        <f t="shared" si="1"/>
+        <v>10939.5</v>
+      </c>
+      <c r="K8" s="167">
+        <v>0</v>
+      </c>
+      <c r="L8" s="167">
+        <v>0</v>
+      </c>
+      <c r="M8" s="167">
+        <v>0</v>
+      </c>
+      <c r="N8" s="167">
+        <v>10939.5</v>
+      </c>
+      <c r="O8" s="167">
         <f t="shared" si="0"/>
         <v>10939.5</v>
       </c>
-      <c r="K8" s="167">
-        <v>0</v>
-      </c>
-      <c r="L8" s="167">
-        <v>0</v>
-      </c>
-      <c r="M8" s="167">
-        <v>0</v>
-      </c>
-      <c r="N8" s="167">
-        <v>10939.5</v>
-      </c>
-      <c r="O8" s="167">
-        <f t="shared" si="1"/>
-        <v>10939.5</v>
-      </c>
       <c r="P8" s="167">
         <v>0</v>
       </c>
@@ -18581,7 +18946,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="160">
         <v>13382</v>
       </c>
@@ -18610,7 +18975,7 @@
         <v>8832.14</v>
       </c>
       <c r="J9" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>8832.14</v>
       </c>
       <c r="K9" s="167">
@@ -18626,7 +18991,7 @@
         <v>1818.14</v>
       </c>
       <c r="O9" s="167">
-        <f t="shared" si="1"/>
+        <f>+H9*N9</f>
         <v>1818.14</v>
       </c>
       <c r="P9" s="167">
@@ -18657,7 +19022,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="160">
         <v>13362</v>
       </c>
@@ -18686,7 +19051,7 @@
         <v>3788.24</v>
       </c>
       <c r="J10" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3788.24</v>
       </c>
       <c r="K10" s="167">
@@ -18702,7 +19067,7 @@
         <v>1511.48</v>
       </c>
       <c r="O10" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1511.48</v>
       </c>
       <c r="P10" s="167">
@@ -18733,7 +19098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="160">
         <v>13356</v>
       </c>
@@ -18762,7 +19127,7 @@
         <v>1712.7</v>
       </c>
       <c r="J11" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1712.7</v>
       </c>
       <c r="K11" s="167">
@@ -18778,7 +19143,7 @@
         <v>1294.67</v>
       </c>
       <c r="O11" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1294.67</v>
       </c>
       <c r="P11" s="167">
@@ -18809,7 +19174,7 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="160">
         <v>13347</v>
       </c>
@@ -18838,7 +19203,7 @@
         <v>26906.17</v>
       </c>
       <c r="J12" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26906.17</v>
       </c>
       <c r="K12" s="167">
@@ -18854,7 +19219,7 @@
         <v>14896.17</v>
       </c>
       <c r="O12" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14896.17</v>
       </c>
       <c r="P12" s="167">
@@ -18885,7 +19250,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="160">
         <v>13346</v>
       </c>
@@ -18914,7 +19279,7 @@
         <v>2282.37</v>
       </c>
       <c r="J13" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2282.37</v>
       </c>
       <c r="K13" s="167">
@@ -18930,7 +19295,7 @@
         <v>532.61</v>
       </c>
       <c r="O13" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>532.61</v>
       </c>
       <c r="P13" s="167">
@@ -18961,7 +19326,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="160">
         <v>13338</v>
       </c>
@@ -18990,7 +19355,7 @@
         <v>0.5</v>
       </c>
       <c r="J14" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.5</v>
       </c>
       <c r="K14" s="167">
@@ -19006,7 +19371,7 @@
         <v>0</v>
       </c>
       <c r="O14" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P14" s="167">
@@ -19066,7 +19431,7 @@
         <v>1471.5</v>
       </c>
       <c r="J15" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1471.5</v>
       </c>
       <c r="K15" s="167">
@@ -19082,7 +19447,7 @@
         <v>900.75</v>
       </c>
       <c r="O15" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>900.75</v>
       </c>
       <c r="P15" s="167">
@@ -19113,7 +19478,7 @@
         <v>0.62</v>
       </c>
     </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="160">
         <v>13298</v>
       </c>
@@ -19142,7 +19507,7 @@
         <v>20250</v>
       </c>
       <c r="J16" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>20250</v>
       </c>
       <c r="K16" s="167">
@@ -19158,7 +19523,7 @@
         <v>14000</v>
       </c>
       <c r="O16" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14000</v>
       </c>
       <c r="P16" s="167">
@@ -19189,7 +19554,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="17" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="160">
         <v>13297</v>
       </c>
@@ -19218,7 +19583,7 @@
         <v>2797.43</v>
       </c>
       <c r="J17" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2797.43</v>
       </c>
       <c r="K17" s="167">
@@ -19234,7 +19599,7 @@
         <v>1549</v>
       </c>
       <c r="O17" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1549</v>
       </c>
       <c r="P17" s="167">
@@ -19265,7 +19630,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="18" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="160">
         <v>13288</v>
       </c>
@@ -19294,7 +19659,7 @@
         <v>5508.81</v>
       </c>
       <c r="J18" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5508.81</v>
       </c>
       <c r="K18" s="167">
@@ -19310,7 +19675,7 @@
         <v>3820.32</v>
       </c>
       <c r="O18" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>3820.32</v>
       </c>
       <c r="P18" s="167">
@@ -19341,7 +19706,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="19" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="160">
         <v>13283</v>
       </c>
@@ -19370,7 +19735,7 @@
         <v>7140.41</v>
       </c>
       <c r="J19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7140.41</v>
       </c>
       <c r="K19" s="167">
@@ -19386,7 +19751,7 @@
         <v>1722.45</v>
       </c>
       <c r="O19" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1722.45</v>
       </c>
       <c r="P19" s="167">
@@ -19417,7 +19782,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="20" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="160">
         <v>13267</v>
       </c>
@@ -19446,7 +19811,7 @@
         <v>14010.74</v>
       </c>
       <c r="J20" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>14010.74</v>
       </c>
       <c r="K20" s="167">
@@ -19462,7 +19827,7 @@
         <v>2637.46</v>
       </c>
       <c r="O20" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2637.46</v>
       </c>
       <c r="P20" s="167">
@@ -19493,7 +19858,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="160">
         <v>13239</v>
       </c>
@@ -19522,7 +19887,7 @@
         <v>38485.39</v>
       </c>
       <c r="J21" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>38485.39</v>
       </c>
       <c r="K21" s="167">
@@ -19538,7 +19903,7 @@
         <v>14731.38</v>
       </c>
       <c r="O21" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>14731.38</v>
       </c>
       <c r="P21" s="167">
@@ -19569,7 +19934,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="22" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="160">
         <v>13237</v>
       </c>
@@ -19598,7 +19963,7 @@
         <v>26803.03</v>
       </c>
       <c r="J22" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>26803.03</v>
       </c>
       <c r="K22" s="167">
@@ -19614,7 +19979,7 @@
         <v>8762.0300000000007</v>
       </c>
       <c r="O22" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8762.0300000000007</v>
       </c>
       <c r="P22" s="167">
@@ -19645,7 +20010,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="23" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="160">
         <v>13231</v>
       </c>
@@ -19674,7 +20039,7 @@
         <v>1878.67</v>
       </c>
       <c r="J23" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1878.67</v>
       </c>
       <c r="K23" s="167">
@@ -19690,7 +20055,7 @@
         <v>973.4</v>
       </c>
       <c r="O23" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>973.4</v>
       </c>
       <c r="P23" s="167">
@@ -19721,7 +20086,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="24" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="160">
         <v>13228</v>
       </c>
@@ -19750,7 +20115,7 @@
         <v>2236.8000000000002</v>
       </c>
       <c r="J24" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2236.8000000000002</v>
       </c>
       <c r="K24" s="167">
@@ -19766,7 +20131,7 @@
         <v>1436</v>
       </c>
       <c r="O24" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1436</v>
       </c>
       <c r="P24" s="167">
@@ -19797,7 +20162,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="25" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="160">
         <v>13219</v>
       </c>
@@ -19826,7 +20191,7 @@
         <v>35391.199999999997</v>
       </c>
       <c r="J25" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>35391.199999999997</v>
       </c>
       <c r="K25" s="167">
@@ -19842,7 +20207,7 @@
         <v>21419.58</v>
       </c>
       <c r="O25" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>21419.58</v>
       </c>
       <c r="P25" s="167">
@@ -19873,7 +20238,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="160">
         <v>13173</v>
       </c>
@@ -19902,7 +20267,7 @@
         <v>7151.29</v>
       </c>
       <c r="J26" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>7151.29</v>
       </c>
       <c r="K26" s="167">
@@ -19918,7 +20283,7 @@
         <v>5199.42</v>
       </c>
       <c r="O26" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>5199.42</v>
       </c>
       <c r="P26" s="167">
@@ -19949,7 +20314,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="27" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="160">
         <v>13170</v>
       </c>
@@ -19978,7 +20343,7 @@
         <v>3035.18</v>
       </c>
       <c r="J27" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3035.18</v>
       </c>
       <c r="K27" s="167">
@@ -19994,7 +20359,7 @@
         <v>1062.06</v>
       </c>
       <c r="O27" s="167">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1062.06</v>
       </c>
       <c r="P27" s="167">
@@ -20025,7 +20390,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="28" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="160">
         <v>13008</v>
       </c>
@@ -20070,7 +20435,7 @@
         <v>228</v>
       </c>
       <c r="O28" s="167">
-        <f t="shared" si="1"/>
+        <f>+H28*N28</f>
         <v>3925.2936</v>
       </c>
       <c r="P28" s="167">
@@ -20101,7 +20466,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="29" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="G29" s="166">
         <f>+AVERAGE(G2:G28)</f>
         <v>17.392199999999999</v>
@@ -20115,14 +20480,14 @@
         <v>291171.06359999999</v>
       </c>
     </row>
-    <row r="30" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
-      <c r="N30" s="169">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="N30" s="181">
         <f>+N28</f>
         <v>228</v>
       </c>
       <c r="O30" s="169"/>
     </row>
-    <row r="31" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="N31" s="170" t="e">
         <f>+N29+N30*#REF!</f>
         <v>#REF!</v>
@@ -20132,17 +20497,3381 @@
     <row r="33" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J33" s="154">
         <f>SUBTOTAL(9,J2:J32)</f>
-        <v>1471.5</v>
+        <v>459673.78523799998</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X31" xr:uid="{8F4EBE57-6C17-4D87-B36A-3DB604C88F7B}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="WOODCRAFTERS HOME PRODUCTS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:X31" xr:uid="{8F4EBE57-6C17-4D87-B36A-3DB604C88F7B}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EFAB7BA-C287-458D-80E8-9131283220CB}">
+  <dimension ref="A1:X45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="11.5546875" style="206"/>
+    <col min="6" max="6" width="9.21875" style="206" customWidth="1"/>
+    <col min="7" max="8" width="11.5546875" style="206"/>
+    <col min="9" max="22" width="17.5546875" style="206" customWidth="1"/>
+    <col min="23" max="16384" width="11.5546875" style="206"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" ht="35.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="109" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="109" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="110" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="109" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="110" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="110" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="213"/>
+      <c r="I1" s="110" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="213"/>
+      <c r="K1" s="162" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="162" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="163" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="164" t="s">
+        <v>10</v>
+      </c>
+      <c r="O1" s="215" t="s">
+        <v>477</v>
+      </c>
+      <c r="P1" s="163" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="162" t="s">
+        <v>12</v>
+      </c>
+      <c r="R1" s="162" t="s">
+        <v>371</v>
+      </c>
+      <c r="S1" s="162" t="s">
+        <v>13</v>
+      </c>
+      <c r="T1" s="162" t="s">
+        <v>235</v>
+      </c>
+      <c r="U1" s="162" t="s">
+        <v>15</v>
+      </c>
+      <c r="V1" s="162" t="s">
+        <v>16</v>
+      </c>
+      <c r="W1" s="162" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="162" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A2" s="208">
+        <v>13659</v>
+      </c>
+      <c r="B2" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E2" s="208" t="s">
+        <v>429</v>
+      </c>
+      <c r="F2" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="210">
+        <v>17.526</v>
+      </c>
+      <c r="H2" s="210">
+        <v>1</v>
+      </c>
+      <c r="I2" s="210">
+        <v>74958.27</v>
+      </c>
+      <c r="J2" s="210">
+        <f>+I2*H2</f>
+        <v>74958.27</v>
+      </c>
+      <c r="K2" s="210">
+        <v>8735.81</v>
+      </c>
+      <c r="L2" s="210">
+        <v>10243.370000000001</v>
+      </c>
+      <c r="M2" s="210">
+        <v>21704.880000000001</v>
+      </c>
+      <c r="N2" s="210">
+        <v>33970.89</v>
+      </c>
+      <c r="O2" s="210">
+        <f>+N2*H2</f>
+        <v>33970.89</v>
+      </c>
+      <c r="P2" s="210">
+        <v>11551.26</v>
+      </c>
+      <c r="Q2" s="210">
+        <v>7731.24</v>
+      </c>
+      <c r="R2" s="210">
+        <v>40987.379999999997</v>
+      </c>
+      <c r="S2" s="210">
+        <v>19282.5</v>
+      </c>
+      <c r="T2" s="210">
+        <v>9039.1299999999992</v>
+      </c>
+      <c r="U2" s="211">
+        <v>0.1206</v>
+      </c>
+      <c r="V2" s="210">
+        <v>9039.1299999999992</v>
+      </c>
+      <c r="W2" s="211">
+        <v>0.1206</v>
+      </c>
+      <c r="X2" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A3" s="208">
+        <v>13652</v>
+      </c>
+      <c r="B3" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="208" t="s">
+        <v>430</v>
+      </c>
+      <c r="D3" s="209">
+        <v>46199</v>
+      </c>
+      <c r="E3" s="208" t="s">
+        <v>431</v>
+      </c>
+      <c r="F3" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="210">
+        <v>17.5505</v>
+      </c>
+      <c r="H3" s="210">
+        <v>1</v>
+      </c>
+      <c r="I3" s="210">
+        <v>10462.59</v>
+      </c>
+      <c r="J3" s="210">
+        <f t="shared" ref="J3:J13" si="0">+I3*H3</f>
+        <v>10462.59</v>
+      </c>
+      <c r="K3" s="210">
+        <v>1784.51</v>
+      </c>
+      <c r="L3" s="210">
+        <v>1461.37</v>
+      </c>
+      <c r="M3" s="210">
+        <v>2994.51</v>
+      </c>
+      <c r="N3" s="210">
+        <v>121.86</v>
+      </c>
+      <c r="O3" s="210">
+        <f t="shared" ref="O3:O44" si="1">+N3*H3</f>
+        <v>121.86</v>
+      </c>
+      <c r="P3" s="210">
+        <v>73.89</v>
+      </c>
+      <c r="Q3" s="210">
+        <v>7272.33</v>
+      </c>
+      <c r="R3" s="210">
+        <v>10340.73</v>
+      </c>
+      <c r="S3" s="210">
+        <v>7346.22</v>
+      </c>
+      <c r="T3" s="210">
+        <v>5884.85</v>
+      </c>
+      <c r="U3" s="211">
+        <v>0.73299999999999998</v>
+      </c>
+      <c r="V3" s="210">
+        <v>5561.71</v>
+      </c>
+      <c r="W3" s="211">
+        <v>0.53159999999999996</v>
+      </c>
+      <c r="X3" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A4" s="208">
+        <v>13640</v>
+      </c>
+      <c r="B4" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="208" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="209">
+        <v>46198</v>
+      </c>
+      <c r="E4" s="208" t="s">
+        <v>432</v>
+      </c>
+      <c r="F4" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="210">
+        <v>17.347999999999999</v>
+      </c>
+      <c r="H4" s="210">
+        <v>1</v>
+      </c>
+      <c r="I4" s="210">
+        <v>4503.7</v>
+      </c>
+      <c r="J4" s="210">
+        <f t="shared" si="0"/>
+        <v>4503.7</v>
+      </c>
+      <c r="K4" s="210">
+        <v>746.96</v>
+      </c>
+      <c r="L4" s="210">
+        <v>747.03</v>
+      </c>
+      <c r="M4" s="210">
+        <v>0</v>
+      </c>
+      <c r="N4" s="210">
+        <v>3106.46</v>
+      </c>
+      <c r="O4" s="210">
+        <f t="shared" si="1"/>
+        <v>3106.46</v>
+      </c>
+      <c r="P4" s="210">
+        <v>1397.24</v>
+      </c>
+      <c r="Q4" s="210">
+        <v>0</v>
+      </c>
+      <c r="R4" s="210">
+        <v>1397.24</v>
+      </c>
+      <c r="S4" s="210">
+        <v>1396.88</v>
+      </c>
+      <c r="T4" s="210">
+        <v>649.85</v>
+      </c>
+      <c r="U4" s="211">
+        <v>0.14430000000000001</v>
+      </c>
+      <c r="V4" s="210">
+        <v>649.85</v>
+      </c>
+      <c r="W4" s="211">
+        <v>0.14430000000000001</v>
+      </c>
+      <c r="X4" s="212">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A5" s="208">
+        <v>13634</v>
+      </c>
+      <c r="B5" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E5" s="208" t="s">
+        <v>433</v>
+      </c>
+      <c r="F5" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="210">
+        <v>17.347999999999999</v>
+      </c>
+      <c r="H5" s="210">
+        <v>1</v>
+      </c>
+      <c r="I5" s="210">
+        <v>92847.8</v>
+      </c>
+      <c r="J5" s="210">
+        <f t="shared" si="0"/>
+        <v>92847.8</v>
+      </c>
+      <c r="K5" s="210">
+        <v>10685.67</v>
+      </c>
+      <c r="L5" s="210">
+        <v>12594.92</v>
+      </c>
+      <c r="M5" s="210">
+        <v>30117.42</v>
+      </c>
+      <c r="N5" s="210">
+        <v>37626.639999999999</v>
+      </c>
+      <c r="O5" s="210">
+        <f t="shared" si="1"/>
+        <v>37626.639999999999</v>
+      </c>
+      <c r="P5" s="210">
+        <v>13169.56</v>
+      </c>
+      <c r="Q5" s="210">
+        <v>11934.18</v>
+      </c>
+      <c r="R5" s="210">
+        <v>55221.16</v>
+      </c>
+      <c r="S5" s="210">
+        <v>25103.74</v>
+      </c>
+      <c r="T5" s="210">
+        <v>12508.82</v>
+      </c>
+      <c r="U5" s="211">
+        <v>0.13469999999999999</v>
+      </c>
+      <c r="V5" s="210">
+        <v>12508.82</v>
+      </c>
+      <c r="W5" s="211">
+        <v>0.13469999999999999</v>
+      </c>
+      <c r="X5" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A6" s="208">
+        <v>13617</v>
+      </c>
+      <c r="B6" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="208" t="s">
+        <v>434</v>
+      </c>
+      <c r="D6" s="209">
+        <v>46197</v>
+      </c>
+      <c r="E6" s="208" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="210">
+        <v>17.3688</v>
+      </c>
+      <c r="H6" s="210">
+        <v>1</v>
+      </c>
+      <c r="I6" s="210">
+        <v>5374.22</v>
+      </c>
+      <c r="J6" s="210">
+        <f t="shared" si="0"/>
+        <v>5374.22</v>
+      </c>
+      <c r="K6" s="210">
+        <v>519.42999999999995</v>
+      </c>
+      <c r="L6" s="210">
+        <v>512.96</v>
+      </c>
+      <c r="M6" s="210">
+        <v>0</v>
+      </c>
+      <c r="N6" s="210">
+        <v>3765.46</v>
+      </c>
+      <c r="O6" s="210">
+        <f t="shared" si="1"/>
+        <v>3765.46</v>
+      </c>
+      <c r="P6" s="210">
+        <v>1608.76</v>
+      </c>
+      <c r="Q6" s="210">
+        <v>0</v>
+      </c>
+      <c r="R6" s="210">
+        <v>1608.76</v>
+      </c>
+      <c r="S6" s="210">
+        <v>1607.02</v>
+      </c>
+      <c r="T6" s="210">
+        <v>1094.06</v>
+      </c>
+      <c r="U6" s="211">
+        <v>0.30020000000000002</v>
+      </c>
+      <c r="V6" s="210">
+        <v>1087.5899999999999</v>
+      </c>
+      <c r="W6" s="211">
+        <v>0.2024</v>
+      </c>
+      <c r="X6" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A7" s="208">
+        <v>13614</v>
+      </c>
+      <c r="B7" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="208" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7" s="209">
+        <v>46199</v>
+      </c>
+      <c r="E7" s="208" t="s">
+        <v>436</v>
+      </c>
+      <c r="F7" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="210">
+        <v>17.1892</v>
+      </c>
+      <c r="H7" s="210">
+        <v>1</v>
+      </c>
+      <c r="I7" s="210">
+        <v>8365.0400000000009</v>
+      </c>
+      <c r="J7" s="210">
+        <f t="shared" si="0"/>
+        <v>8365.0400000000009</v>
+      </c>
+      <c r="K7" s="210">
+        <v>667.3</v>
+      </c>
+      <c r="L7" s="210">
+        <v>692.88</v>
+      </c>
+      <c r="M7" s="210">
+        <v>0</v>
+      </c>
+      <c r="N7" s="210">
+        <v>6429.32</v>
+      </c>
+      <c r="O7" s="210">
+        <f t="shared" si="1"/>
+        <v>6429.32</v>
+      </c>
+      <c r="P7" s="210">
+        <v>1935.72</v>
+      </c>
+      <c r="Q7" s="210">
+        <v>0</v>
+      </c>
+      <c r="R7" s="210">
+        <v>1935.72</v>
+      </c>
+      <c r="S7" s="210">
+        <v>1935.72</v>
+      </c>
+      <c r="T7" s="210">
+        <v>1242.8399999999999</v>
+      </c>
+      <c r="U7" s="211">
+        <v>0.14860000000000001</v>
+      </c>
+      <c r="V7" s="210">
+        <v>1242.8399999999999</v>
+      </c>
+      <c r="W7" s="211">
+        <v>0.14860000000000001</v>
+      </c>
+      <c r="X7" s="212">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A8" s="208">
+        <v>13611</v>
+      </c>
+      <c r="B8" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="208" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="209">
+        <v>46203</v>
+      </c>
+      <c r="E8" s="208" t="s">
+        <v>437</v>
+      </c>
+      <c r="F8" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="210">
+        <v>17.1892</v>
+      </c>
+      <c r="H8" s="210">
+        <v>1</v>
+      </c>
+      <c r="I8" s="210">
+        <v>5753.36</v>
+      </c>
+      <c r="J8" s="210">
+        <f t="shared" si="0"/>
+        <v>5753.36</v>
+      </c>
+      <c r="K8" s="210">
+        <v>515.07000000000005</v>
+      </c>
+      <c r="L8" s="210">
+        <v>519.64</v>
+      </c>
+      <c r="M8" s="210">
+        <v>0</v>
+      </c>
+      <c r="N8" s="210">
+        <v>3987.84</v>
+      </c>
+      <c r="O8" s="210">
+        <f t="shared" si="1"/>
+        <v>3987.84</v>
+      </c>
+      <c r="P8" s="210">
+        <v>1765.52</v>
+      </c>
+      <c r="Q8" s="210">
+        <v>0</v>
+      </c>
+      <c r="R8" s="210">
+        <v>1765.52</v>
+      </c>
+      <c r="S8" s="210">
+        <v>1764.48</v>
+      </c>
+      <c r="T8" s="210">
+        <v>1244.8399999999999</v>
+      </c>
+      <c r="U8" s="211">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="V8" s="210">
+        <v>1244.8399999999999</v>
+      </c>
+      <c r="W8" s="211">
+        <v>0.21640000000000001</v>
+      </c>
+      <c r="X8" s="212">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A9" s="208">
+        <v>13606</v>
+      </c>
+      <c r="B9" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="208" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="209">
+        <v>46195</v>
+      </c>
+      <c r="E9" s="208" t="s">
+        <v>252</v>
+      </c>
+      <c r="F9" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="210">
+        <v>17.202300000000001</v>
+      </c>
+      <c r="H9" s="210">
+        <v>1</v>
+      </c>
+      <c r="I9" s="210">
+        <v>2371.1999999999998</v>
+      </c>
+      <c r="J9" s="210">
+        <f t="shared" si="0"/>
+        <v>2371.1999999999998</v>
+      </c>
+      <c r="K9" s="210">
+        <v>487.12</v>
+      </c>
+      <c r="L9" s="210">
+        <v>415.14</v>
+      </c>
+      <c r="M9" s="210">
+        <v>0</v>
+      </c>
+      <c r="N9" s="210">
+        <v>1032.1500000000001</v>
+      </c>
+      <c r="O9" s="210">
+        <f t="shared" si="1"/>
+        <v>1032.1500000000001</v>
+      </c>
+      <c r="P9" s="210">
+        <v>1339.05</v>
+      </c>
+      <c r="Q9" s="210">
+        <v>0</v>
+      </c>
+      <c r="R9" s="210">
+        <v>1339.05</v>
+      </c>
+      <c r="S9" s="210">
+        <v>1239.05</v>
+      </c>
+      <c r="T9" s="210">
+        <v>823.91</v>
+      </c>
+      <c r="U9" s="211">
+        <v>0.55289999999999995</v>
+      </c>
+      <c r="V9" s="210">
+        <v>751.93</v>
+      </c>
+      <c r="W9" s="211">
+        <v>0.31709999999999999</v>
+      </c>
+      <c r="X9" s="212">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A10" s="208">
+        <v>13600</v>
+      </c>
+      <c r="B10" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="208" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="209">
+        <v>46198</v>
+      </c>
+      <c r="E10" s="208" t="s">
+        <v>438</v>
+      </c>
+      <c r="F10" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="210">
+        <v>17.202300000000001</v>
+      </c>
+      <c r="H10" s="210">
+        <v>1</v>
+      </c>
+      <c r="I10" s="210">
+        <v>3999.98</v>
+      </c>
+      <c r="J10" s="210">
+        <f t="shared" si="0"/>
+        <v>3999.98</v>
+      </c>
+      <c r="K10" s="210">
+        <v>510</v>
+      </c>
+      <c r="L10" s="210">
+        <v>358.82</v>
+      </c>
+      <c r="M10" s="210">
+        <v>706.62</v>
+      </c>
+      <c r="N10" s="210">
+        <v>211.99</v>
+      </c>
+      <c r="O10" s="210">
+        <f t="shared" si="1"/>
+        <v>211.99</v>
+      </c>
+      <c r="P10" s="208" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q10" s="210">
+        <v>3293.36</v>
+      </c>
+      <c r="R10" s="210">
+        <v>3787.99</v>
+      </c>
+      <c r="S10" s="210">
+        <v>3081.37</v>
+      </c>
+      <c r="T10" s="210">
+        <v>2722.55</v>
+      </c>
+      <c r="U10" s="211">
+        <v>0.80810000000000004</v>
+      </c>
+      <c r="V10" s="210">
+        <v>2571.37</v>
+      </c>
+      <c r="W10" s="211">
+        <v>0.64280000000000004</v>
+      </c>
+      <c r="X10" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A11" s="208">
+        <v>13579</v>
+      </c>
+      <c r="B11" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="208" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="209">
+        <v>46203</v>
+      </c>
+      <c r="E11" s="208" t="s">
+        <v>440</v>
+      </c>
+      <c r="F11" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="210">
+        <v>17.206700000000001</v>
+      </c>
+      <c r="H11" s="210">
+        <v>1</v>
+      </c>
+      <c r="I11" s="210">
+        <v>10176.969999999999</v>
+      </c>
+      <c r="J11" s="210">
+        <f t="shared" si="0"/>
+        <v>10176.969999999999</v>
+      </c>
+      <c r="K11" s="210">
+        <v>1205.3699999999999</v>
+      </c>
+      <c r="L11" s="210">
+        <v>1146.18</v>
+      </c>
+      <c r="M11" s="210">
+        <v>2212.54</v>
+      </c>
+      <c r="N11" s="210">
+        <v>2697.13</v>
+      </c>
+      <c r="O11" s="210">
+        <f t="shared" si="1"/>
+        <v>2697.13</v>
+      </c>
+      <c r="P11" s="210">
+        <v>1782.05</v>
+      </c>
+      <c r="Q11" s="210">
+        <v>3485.25</v>
+      </c>
+      <c r="R11" s="210">
+        <v>7479.84</v>
+      </c>
+      <c r="S11" s="210">
+        <v>5267.3</v>
+      </c>
+      <c r="T11" s="210">
+        <v>4121.12</v>
+      </c>
+      <c r="U11" s="211">
+        <v>0.52339999999999998</v>
+      </c>
+      <c r="V11" s="210">
+        <v>4061.93</v>
+      </c>
+      <c r="W11" s="211">
+        <v>0.39910000000000001</v>
+      </c>
+      <c r="X11" s="212">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A12" s="208">
+        <v>13576</v>
+      </c>
+      <c r="B12" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="208" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="209">
+        <v>46190</v>
+      </c>
+      <c r="E12" s="208" t="s">
+        <v>441</v>
+      </c>
+      <c r="F12" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G12" s="210">
+        <v>17.206700000000001</v>
+      </c>
+      <c r="H12" s="210">
+        <v>1</v>
+      </c>
+      <c r="I12" s="210">
+        <v>10939.5</v>
+      </c>
+      <c r="J12" s="210">
+        <f t="shared" si="0"/>
+        <v>10939.5</v>
+      </c>
+      <c r="K12" s="210">
+        <v>0</v>
+      </c>
+      <c r="L12" s="210">
+        <v>0</v>
+      </c>
+      <c r="M12" s="210">
+        <v>0</v>
+      </c>
+      <c r="N12" s="210">
+        <v>10939.5</v>
+      </c>
+      <c r="O12" s="210">
+        <f t="shared" si="1"/>
+        <v>10939.5</v>
+      </c>
+      <c r="P12" s="210">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="210">
+        <v>0</v>
+      </c>
+      <c r="R12" s="210">
+        <v>0</v>
+      </c>
+      <c r="S12" s="210">
+        <v>0</v>
+      </c>
+      <c r="T12" s="210">
+        <v>0</v>
+      </c>
+      <c r="U12" s="211">
+        <v>0</v>
+      </c>
+      <c r="V12" s="210">
+        <v>0</v>
+      </c>
+      <c r="W12" s="211">
+        <v>0</v>
+      </c>
+      <c r="X12" s="212">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A13" s="208">
+        <v>13549</v>
+      </c>
+      <c r="B13" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="208" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="209">
+        <v>46185</v>
+      </c>
+      <c r="E13" s="208" t="s">
+        <v>442</v>
+      </c>
+      <c r="F13" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="210">
+        <v>17.4453</v>
+      </c>
+      <c r="H13" s="210">
+        <v>1</v>
+      </c>
+      <c r="I13" s="210">
+        <v>3488.04</v>
+      </c>
+      <c r="J13" s="210">
+        <f t="shared" si="0"/>
+        <v>3488.04</v>
+      </c>
+      <c r="K13" s="210">
+        <v>510.69</v>
+      </c>
+      <c r="L13" s="210">
+        <v>393.6</v>
+      </c>
+      <c r="M13" s="210">
+        <v>0</v>
+      </c>
+      <c r="N13" s="210">
+        <v>1040.04</v>
+      </c>
+      <c r="O13" s="210">
+        <f t="shared" si="1"/>
+        <v>1040.04</v>
+      </c>
+      <c r="P13" s="210">
+        <v>2448</v>
+      </c>
+      <c r="Q13" s="210">
+        <v>0</v>
+      </c>
+      <c r="R13" s="210">
+        <v>2448</v>
+      </c>
+      <c r="S13" s="210">
+        <v>2448</v>
+      </c>
+      <c r="T13" s="210">
+        <v>2054.4</v>
+      </c>
+      <c r="U13" s="211">
+        <v>0.73540000000000005</v>
+      </c>
+      <c r="V13" s="210">
+        <v>1937.31</v>
+      </c>
+      <c r="W13" s="211">
+        <v>0.5554</v>
+      </c>
+      <c r="X13" s="212">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A14" s="208">
+        <v>13539</v>
+      </c>
+      <c r="B14" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="208" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="209">
+        <v>46189</v>
+      </c>
+      <c r="E14" s="208" t="s">
+        <v>268</v>
+      </c>
+      <c r="F14" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G14" s="210">
+        <v>17.4755</v>
+      </c>
+      <c r="H14" s="210">
+        <v>1</v>
+      </c>
+      <c r="I14" s="210">
+        <v>2652.53</v>
+      </c>
+      <c r="J14" s="210">
+        <f>+I14*G14</f>
+        <v>46354.288015000006</v>
+      </c>
+      <c r="K14" s="210">
+        <v>279.77</v>
+      </c>
+      <c r="L14" s="210">
+        <v>235.77</v>
+      </c>
+      <c r="M14" s="210">
+        <v>0</v>
+      </c>
+      <c r="N14" s="210">
+        <v>1382.75</v>
+      </c>
+      <c r="O14" s="210">
+        <f>+N14*G14</f>
+        <v>24164.247625</v>
+      </c>
+      <c r="P14" s="210">
+        <v>1269.78</v>
+      </c>
+      <c r="Q14" s="210">
+        <v>0</v>
+      </c>
+      <c r="R14" s="210">
+        <v>1269.78</v>
+      </c>
+      <c r="S14" s="210">
+        <v>1269.78</v>
+      </c>
+      <c r="T14" s="210">
+        <v>1034.01</v>
+      </c>
+      <c r="U14" s="211">
+        <v>0.49530000000000002</v>
+      </c>
+      <c r="V14" s="210">
+        <v>990.01</v>
+      </c>
+      <c r="W14" s="211">
+        <v>0.37319999999999998</v>
+      </c>
+      <c r="X14" s="212">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A15" s="208">
+        <v>13530</v>
+      </c>
+      <c r="B15" s="208" t="s">
+        <v>316</v>
+      </c>
+      <c r="C15" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="209">
+        <v>46191</v>
+      </c>
+      <c r="E15" s="208" t="s">
+        <v>443</v>
+      </c>
+      <c r="F15" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" s="210">
+        <v>17.332799999999999</v>
+      </c>
+      <c r="H15" s="210">
+        <v>1</v>
+      </c>
+      <c r="I15" s="210">
+        <v>5605.6</v>
+      </c>
+      <c r="J15" s="210">
+        <f t="shared" ref="J15:J27" si="2">+I15*H15</f>
+        <v>5605.6</v>
+      </c>
+      <c r="K15" s="210">
+        <v>994.8</v>
+      </c>
+      <c r="L15" s="210">
+        <v>994.8</v>
+      </c>
+      <c r="M15" s="210">
+        <v>0</v>
+      </c>
+      <c r="N15" s="210">
+        <v>3920</v>
+      </c>
+      <c r="O15" s="210">
+        <f t="shared" si="1"/>
+        <v>3920</v>
+      </c>
+      <c r="P15" s="210">
+        <v>1685.6</v>
+      </c>
+      <c r="Q15" s="210">
+        <v>0</v>
+      </c>
+      <c r="R15" s="210">
+        <v>1685.6</v>
+      </c>
+      <c r="S15" s="210">
+        <v>1685.6</v>
+      </c>
+      <c r="T15" s="210">
+        <v>690.8</v>
+      </c>
+      <c r="U15" s="211">
+        <v>0.30070000000000002</v>
+      </c>
+      <c r="V15" s="210">
+        <v>690.8</v>
+      </c>
+      <c r="W15" s="211">
+        <v>0.1232</v>
+      </c>
+      <c r="X15" s="212">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A16" s="208">
+        <v>13529</v>
+      </c>
+      <c r="B16" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="208" t="s">
+        <v>155</v>
+      </c>
+      <c r="D16" s="209">
+        <v>46197</v>
+      </c>
+      <c r="E16" s="208" t="s">
+        <v>444</v>
+      </c>
+      <c r="F16" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="210">
+        <v>17.332799999999999</v>
+      </c>
+      <c r="H16" s="210">
+        <v>1</v>
+      </c>
+      <c r="I16" s="210">
+        <v>42885.48</v>
+      </c>
+      <c r="J16" s="210">
+        <f t="shared" si="2"/>
+        <v>42885.48</v>
+      </c>
+      <c r="K16" s="210">
+        <v>1401.02</v>
+      </c>
+      <c r="L16" s="210">
+        <v>1382.88</v>
+      </c>
+      <c r="M16" s="210">
+        <v>0</v>
+      </c>
+      <c r="N16" s="210">
+        <v>29429.26</v>
+      </c>
+      <c r="O16" s="210">
+        <f t="shared" si="1"/>
+        <v>29429.26</v>
+      </c>
+      <c r="P16" s="210">
+        <v>13456.22</v>
+      </c>
+      <c r="Q16" s="210">
+        <v>0</v>
+      </c>
+      <c r="R16" s="210">
+        <v>13456.22</v>
+      </c>
+      <c r="S16" s="210">
+        <v>9626.16</v>
+      </c>
+      <c r="T16" s="210">
+        <v>8243.2800000000007</v>
+      </c>
+      <c r="U16" s="211">
+        <v>0.22489999999999999</v>
+      </c>
+      <c r="V16" s="210">
+        <v>8225.14</v>
+      </c>
+      <c r="W16" s="211">
+        <v>0.1918</v>
+      </c>
+      <c r="X16" s="212">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A17" s="208">
+        <v>13523</v>
+      </c>
+      <c r="B17" s="208" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="209">
+        <v>46199</v>
+      </c>
+      <c r="E17" s="208" t="s">
+        <v>445</v>
+      </c>
+      <c r="F17" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="210">
+        <v>17.294499999999999</v>
+      </c>
+      <c r="H17" s="210">
+        <v>1</v>
+      </c>
+      <c r="I17" s="210">
+        <v>24000</v>
+      </c>
+      <c r="J17" s="210">
+        <f t="shared" si="2"/>
+        <v>24000</v>
+      </c>
+      <c r="K17" s="210">
+        <v>2170</v>
+      </c>
+      <c r="L17" s="210">
+        <v>1822.42</v>
+      </c>
+      <c r="M17" s="210">
+        <v>0</v>
+      </c>
+      <c r="N17" s="210">
+        <v>9827.64</v>
+      </c>
+      <c r="O17" s="210">
+        <f t="shared" si="1"/>
+        <v>9827.64</v>
+      </c>
+      <c r="P17" s="210">
+        <v>14172.36</v>
+      </c>
+      <c r="Q17" s="210">
+        <v>0</v>
+      </c>
+      <c r="R17" s="210">
+        <v>14172.36</v>
+      </c>
+      <c r="S17" s="210">
+        <v>14172.36</v>
+      </c>
+      <c r="T17" s="210">
+        <v>12349.94</v>
+      </c>
+      <c r="U17" s="211">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="V17" s="210">
+        <v>12002.36</v>
+      </c>
+      <c r="W17" s="211">
+        <v>0.50009999999999999</v>
+      </c>
+      <c r="X17" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A18" s="208">
+        <v>13510</v>
+      </c>
+      <c r="B18" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="208" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="209">
+        <v>46203</v>
+      </c>
+      <c r="E18" s="208" t="s">
+        <v>446</v>
+      </c>
+      <c r="F18" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="210">
+        <v>17.378</v>
+      </c>
+      <c r="H18" s="210">
+        <v>1</v>
+      </c>
+      <c r="I18" s="210">
+        <v>28768.01</v>
+      </c>
+      <c r="J18" s="210">
+        <f t="shared" si="2"/>
+        <v>28768.01</v>
+      </c>
+      <c r="K18" s="210">
+        <v>3400.48</v>
+      </c>
+      <c r="L18" s="210">
+        <v>2916.08</v>
+      </c>
+      <c r="M18" s="210">
+        <v>1912.27</v>
+      </c>
+      <c r="N18" s="210">
+        <v>12590.6</v>
+      </c>
+      <c r="O18" s="210">
+        <f t="shared" si="1"/>
+        <v>12590.6</v>
+      </c>
+      <c r="P18" s="210">
+        <v>8427.15</v>
+      </c>
+      <c r="Q18" s="210">
+        <v>5837.99</v>
+      </c>
+      <c r="R18" s="210">
+        <v>16177.41</v>
+      </c>
+      <c r="S18" s="210">
+        <v>14080.44</v>
+      </c>
+      <c r="T18" s="210">
+        <v>11164.36</v>
+      </c>
+      <c r="U18" s="211">
+        <v>0.50629999999999997</v>
+      </c>
+      <c r="V18" s="210">
+        <v>10679.96</v>
+      </c>
+      <c r="W18" s="211">
+        <v>0.37119999999999997</v>
+      </c>
+      <c r="X18" s="212">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A19" s="208">
+        <v>13505</v>
+      </c>
+      <c r="B19" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="208" t="s">
+        <v>261</v>
+      </c>
+      <c r="D19" s="209">
+        <v>46196</v>
+      </c>
+      <c r="E19" s="208" t="s">
+        <v>447</v>
+      </c>
+      <c r="F19" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" s="210">
+        <v>17.3505</v>
+      </c>
+      <c r="H19" s="210">
+        <v>1</v>
+      </c>
+      <c r="I19" s="210">
+        <v>8739.56</v>
+      </c>
+      <c r="J19" s="210">
+        <f t="shared" si="2"/>
+        <v>8739.56</v>
+      </c>
+      <c r="K19" s="210">
+        <v>1022.89</v>
+      </c>
+      <c r="L19" s="210">
+        <v>888.29</v>
+      </c>
+      <c r="M19" s="210">
+        <v>0</v>
+      </c>
+      <c r="N19" s="210">
+        <v>4909.8599999999997</v>
+      </c>
+      <c r="O19" s="210">
+        <f t="shared" si="1"/>
+        <v>4909.8599999999997</v>
+      </c>
+      <c r="P19" s="210">
+        <v>3829.7</v>
+      </c>
+      <c r="Q19" s="210">
+        <v>0</v>
+      </c>
+      <c r="R19" s="210">
+        <v>3829.7</v>
+      </c>
+      <c r="S19" s="210">
+        <v>3829.7</v>
+      </c>
+      <c r="T19" s="210">
+        <v>2941.41</v>
+      </c>
+      <c r="U19" s="211">
+        <v>0.4536</v>
+      </c>
+      <c r="V19" s="210">
+        <v>2806.81</v>
+      </c>
+      <c r="W19" s="211">
+        <v>0.32119999999999999</v>
+      </c>
+      <c r="X19" s="212">
+        <v>0.47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A20" s="208">
+        <v>13504</v>
+      </c>
+      <c r="B20" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="208" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E20" s="208" t="s">
+        <v>448</v>
+      </c>
+      <c r="F20" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="210">
+        <v>17.3505</v>
+      </c>
+      <c r="H20" s="210">
+        <v>1</v>
+      </c>
+      <c r="I20" s="210">
+        <v>105183.52</v>
+      </c>
+      <c r="J20" s="210">
+        <f t="shared" si="2"/>
+        <v>105183.52</v>
+      </c>
+      <c r="K20" s="210">
+        <v>12204.04</v>
+      </c>
+      <c r="L20" s="210">
+        <v>14466.84</v>
+      </c>
+      <c r="M20" s="210">
+        <v>29974.01</v>
+      </c>
+      <c r="N20" s="210">
+        <v>49514.38</v>
+      </c>
+      <c r="O20" s="210">
+        <f t="shared" si="1"/>
+        <v>49514.38</v>
+      </c>
+      <c r="P20" s="210">
+        <v>17822.7</v>
+      </c>
+      <c r="Q20" s="210">
+        <v>7872.43</v>
+      </c>
+      <c r="R20" s="210">
+        <v>55669.14</v>
+      </c>
+      <c r="S20" s="210">
+        <v>25695.13</v>
+      </c>
+      <c r="T20" s="210">
+        <v>11228.29</v>
+      </c>
+      <c r="U20" s="211">
+        <v>0.1067</v>
+      </c>
+      <c r="V20" s="210">
+        <v>11228.29</v>
+      </c>
+      <c r="W20" s="211">
+        <v>0.1067</v>
+      </c>
+      <c r="X20" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A21" s="208">
+        <v>13497</v>
+      </c>
+      <c r="B21" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="208" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="209">
+        <v>46199</v>
+      </c>
+      <c r="E21" s="208" t="s">
+        <v>449</v>
+      </c>
+      <c r="F21" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" s="210">
+        <v>17.321300000000001</v>
+      </c>
+      <c r="H21" s="210">
+        <v>1</v>
+      </c>
+      <c r="I21" s="210">
+        <v>22463.25</v>
+      </c>
+      <c r="J21" s="210">
+        <f t="shared" si="2"/>
+        <v>22463.25</v>
+      </c>
+      <c r="K21" s="210">
+        <v>2197.16</v>
+      </c>
+      <c r="L21" s="210">
+        <v>2900.57</v>
+      </c>
+      <c r="M21" s="210">
+        <v>0</v>
+      </c>
+      <c r="N21" s="210">
+        <v>16566.07</v>
+      </c>
+      <c r="O21" s="210">
+        <f t="shared" si="1"/>
+        <v>16566.07</v>
+      </c>
+      <c r="P21" s="210">
+        <v>5897.18</v>
+      </c>
+      <c r="Q21" s="210">
+        <v>0</v>
+      </c>
+      <c r="R21" s="210">
+        <v>5897.18</v>
+      </c>
+      <c r="S21" s="210">
+        <v>5897.18</v>
+      </c>
+      <c r="T21" s="210">
+        <v>2996.61</v>
+      </c>
+      <c r="U21" s="211">
+        <v>0.13339999999999999</v>
+      </c>
+      <c r="V21" s="210">
+        <v>2996.61</v>
+      </c>
+      <c r="W21" s="211">
+        <v>0.13339999999999999</v>
+      </c>
+      <c r="X21" s="212">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A22" s="208">
+        <v>13479</v>
+      </c>
+      <c r="B22" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="208" t="s">
+        <v>434</v>
+      </c>
+      <c r="D22" s="209">
+        <v>46198</v>
+      </c>
+      <c r="E22" s="208" t="s">
+        <v>450</v>
+      </c>
+      <c r="F22" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="210">
+        <v>17.3232</v>
+      </c>
+      <c r="H22" s="210">
+        <v>1</v>
+      </c>
+      <c r="I22" s="210">
+        <v>20810.62</v>
+      </c>
+      <c r="J22" s="210">
+        <f t="shared" si="2"/>
+        <v>20810.62</v>
+      </c>
+      <c r="K22" s="210">
+        <v>862.46</v>
+      </c>
+      <c r="L22" s="210">
+        <v>577.13</v>
+      </c>
+      <c r="M22" s="210">
+        <v>0</v>
+      </c>
+      <c r="N22" s="210">
+        <v>5904.25</v>
+      </c>
+      <c r="O22" s="210">
+        <f t="shared" si="1"/>
+        <v>5904.25</v>
+      </c>
+      <c r="P22" s="210">
+        <v>14906.37</v>
+      </c>
+      <c r="Q22" s="210">
+        <v>0</v>
+      </c>
+      <c r="R22" s="210">
+        <v>14906.37</v>
+      </c>
+      <c r="S22" s="210">
+        <v>14904.63</v>
+      </c>
+      <c r="T22" s="210">
+        <v>14327.5</v>
+      </c>
+      <c r="U22" s="211">
+        <v>0.72989999999999999</v>
+      </c>
+      <c r="V22" s="210">
+        <v>14042.17</v>
+      </c>
+      <c r="W22" s="211">
+        <v>0.67479999999999996</v>
+      </c>
+      <c r="X22" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A23" s="208">
+        <v>13473</v>
+      </c>
+      <c r="B23" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="208" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="209">
+        <v>46182</v>
+      </c>
+      <c r="E23" s="208" t="s">
+        <v>451</v>
+      </c>
+      <c r="F23" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="210">
+        <v>17.271999999999998</v>
+      </c>
+      <c r="H23" s="210">
+        <v>1</v>
+      </c>
+      <c r="I23" s="210">
+        <v>11446.4</v>
+      </c>
+      <c r="J23" s="210">
+        <f t="shared" si="2"/>
+        <v>11446.4</v>
+      </c>
+      <c r="K23" s="210">
+        <v>2195.85</v>
+      </c>
+      <c r="L23" s="210">
+        <v>2906.25</v>
+      </c>
+      <c r="M23" s="210">
+        <v>8106.62</v>
+      </c>
+      <c r="N23" s="210">
+        <v>1274.1300000000001</v>
+      </c>
+      <c r="O23" s="210">
+        <f t="shared" si="1"/>
+        <v>1274.1300000000001</v>
+      </c>
+      <c r="P23" s="210">
+        <v>1546.61</v>
+      </c>
+      <c r="Q23" s="210">
+        <v>519.04</v>
+      </c>
+      <c r="R23" s="210">
+        <v>10172.27</v>
+      </c>
+      <c r="S23" s="210">
+        <v>2065.65</v>
+      </c>
+      <c r="T23" s="208" t="s">
+        <v>452</v>
+      </c>
+      <c r="U23" s="208" t="s">
+        <v>453</v>
+      </c>
+      <c r="V23" s="208" t="s">
+        <v>452</v>
+      </c>
+      <c r="W23" s="208" t="s">
+        <v>453</v>
+      </c>
+      <c r="X23" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A24" s="208">
+        <v>13468</v>
+      </c>
+      <c r="B24" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="208" t="s">
+        <v>454</v>
+      </c>
+      <c r="D24" s="209">
+        <v>46190</v>
+      </c>
+      <c r="E24" s="208" t="s">
+        <v>455</v>
+      </c>
+      <c r="F24" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="210">
+        <v>17.271999999999998</v>
+      </c>
+      <c r="H24" s="210">
+        <v>1</v>
+      </c>
+      <c r="I24" s="210">
+        <v>5318.39</v>
+      </c>
+      <c r="J24" s="210">
+        <f t="shared" si="2"/>
+        <v>5318.39</v>
+      </c>
+      <c r="K24" s="210">
+        <v>775.7</v>
+      </c>
+      <c r="L24" s="210">
+        <v>729.34</v>
+      </c>
+      <c r="M24" s="210">
+        <v>2028.3</v>
+      </c>
+      <c r="N24" s="210">
+        <v>333.72</v>
+      </c>
+      <c r="O24" s="210">
+        <f t="shared" si="1"/>
+        <v>333.72</v>
+      </c>
+      <c r="P24" s="210">
+        <v>448.93</v>
+      </c>
+      <c r="Q24" s="210">
+        <v>2507.44</v>
+      </c>
+      <c r="R24" s="210">
+        <v>4984.67</v>
+      </c>
+      <c r="S24" s="210">
+        <v>2956.37</v>
+      </c>
+      <c r="T24" s="210">
+        <v>2227.0300000000002</v>
+      </c>
+      <c r="U24" s="211">
+        <v>0.56459999999999999</v>
+      </c>
+      <c r="V24" s="210">
+        <v>2180.67</v>
+      </c>
+      <c r="W24" s="211">
+        <v>0.41</v>
+      </c>
+      <c r="X24" s="212">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A25" s="208">
+        <v>13457</v>
+      </c>
+      <c r="B25" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="208" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="209">
+        <v>46176</v>
+      </c>
+      <c r="E25" s="208" t="s">
+        <v>456</v>
+      </c>
+      <c r="F25" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="210">
+        <v>17.330500000000001</v>
+      </c>
+      <c r="H25" s="210">
+        <v>1</v>
+      </c>
+      <c r="I25" s="210">
+        <v>7126.8</v>
+      </c>
+      <c r="J25" s="210">
+        <f t="shared" si="2"/>
+        <v>7126.8</v>
+      </c>
+      <c r="K25" s="210">
+        <v>1010.2</v>
+      </c>
+      <c r="L25" s="210">
+        <v>935.48</v>
+      </c>
+      <c r="M25" s="210">
+        <v>0</v>
+      </c>
+      <c r="N25" s="210">
+        <v>4284.22</v>
+      </c>
+      <c r="O25" s="210">
+        <f t="shared" si="1"/>
+        <v>4284.22</v>
+      </c>
+      <c r="P25" s="210">
+        <v>2842.58</v>
+      </c>
+      <c r="Q25" s="210">
+        <v>0</v>
+      </c>
+      <c r="R25" s="210">
+        <v>2842.58</v>
+      </c>
+      <c r="S25" s="210">
+        <v>2842.58</v>
+      </c>
+      <c r="T25" s="210">
+        <v>1907.1</v>
+      </c>
+      <c r="U25" s="211">
+        <v>0.4093</v>
+      </c>
+      <c r="V25" s="210">
+        <v>1832.38</v>
+      </c>
+      <c r="W25" s="211">
+        <v>0.2571</v>
+      </c>
+      <c r="X25" s="212">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A26" s="208">
+        <v>13445</v>
+      </c>
+      <c r="B26" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" s="208" t="s">
+        <v>169</v>
+      </c>
+      <c r="D26" s="209">
+        <v>46176</v>
+      </c>
+      <c r="E26" s="208" t="s">
+        <v>457</v>
+      </c>
+      <c r="F26" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="210">
+        <v>17.293800000000001</v>
+      </c>
+      <c r="H26" s="210">
+        <v>1</v>
+      </c>
+      <c r="I26" s="210">
+        <v>10289.98</v>
+      </c>
+      <c r="J26" s="210">
+        <f t="shared" si="2"/>
+        <v>10289.98</v>
+      </c>
+      <c r="K26" s="210">
+        <v>1220.75</v>
+      </c>
+      <c r="L26" s="210">
+        <v>1203.19</v>
+      </c>
+      <c r="M26" s="210">
+        <v>0</v>
+      </c>
+      <c r="N26" s="210">
+        <v>6354.59</v>
+      </c>
+      <c r="O26" s="210">
+        <f t="shared" si="1"/>
+        <v>6354.59</v>
+      </c>
+      <c r="P26" s="210">
+        <v>3935.39</v>
+      </c>
+      <c r="Q26" s="210">
+        <v>0</v>
+      </c>
+      <c r="R26" s="210">
+        <v>3935.39</v>
+      </c>
+      <c r="S26" s="210">
+        <v>3935.39</v>
+      </c>
+      <c r="T26" s="210">
+        <v>2732.2</v>
+      </c>
+      <c r="U26" s="211">
+        <v>0.38419999999999999</v>
+      </c>
+      <c r="V26" s="210">
+        <v>2714.64</v>
+      </c>
+      <c r="W26" s="211">
+        <v>0.26379999999999998</v>
+      </c>
+      <c r="X26" s="212">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A27" s="208">
+        <v>13443</v>
+      </c>
+      <c r="B27" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="208" t="s">
+        <v>458</v>
+      </c>
+      <c r="D27" s="209">
+        <v>46182</v>
+      </c>
+      <c r="E27" s="208" t="s">
+        <v>459</v>
+      </c>
+      <c r="F27" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="210">
+        <v>17.396799999999999</v>
+      </c>
+      <c r="H27" s="210">
+        <v>1</v>
+      </c>
+      <c r="I27" s="210">
+        <v>7211.78</v>
+      </c>
+      <c r="J27" s="210">
+        <f t="shared" si="2"/>
+        <v>7211.78</v>
+      </c>
+      <c r="K27" s="210">
+        <v>1013.7</v>
+      </c>
+      <c r="L27" s="210">
+        <v>594.98</v>
+      </c>
+      <c r="M27" s="210">
+        <v>1642.78</v>
+      </c>
+      <c r="N27" s="210">
+        <v>0</v>
+      </c>
+      <c r="O27" s="210">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="P27" s="210">
+        <v>695.1</v>
+      </c>
+      <c r="Q27" s="210">
+        <v>4873.8999999999996</v>
+      </c>
+      <c r="R27" s="210">
+        <v>7211.78</v>
+      </c>
+      <c r="S27" s="210">
+        <v>5569</v>
+      </c>
+      <c r="T27" s="210">
+        <v>4974.0200000000004</v>
+      </c>
+      <c r="U27" s="211">
+        <v>0.83030000000000004</v>
+      </c>
+      <c r="V27" s="210">
+        <v>4555.3</v>
+      </c>
+      <c r="W27" s="211">
+        <v>0.63160000000000005</v>
+      </c>
+      <c r="X27" s="212">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A28" s="208">
+        <v>13436</v>
+      </c>
+      <c r="B28" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" s="208" t="s">
+        <v>460</v>
+      </c>
+      <c r="D28" s="209">
+        <v>46191</v>
+      </c>
+      <c r="E28" s="208" t="s">
+        <v>461</v>
+      </c>
+      <c r="F28" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="210">
+        <v>17.2928</v>
+      </c>
+      <c r="H28" s="210">
+        <v>1</v>
+      </c>
+      <c r="I28" s="210">
+        <v>2726.58</v>
+      </c>
+      <c r="J28" s="210">
+        <f>+I28*G28</f>
+        <v>47150.202623999998</v>
+      </c>
+      <c r="K28" s="210">
+        <v>296.85000000000002</v>
+      </c>
+      <c r="L28" s="210">
+        <v>255.77</v>
+      </c>
+      <c r="M28" s="210">
+        <v>0</v>
+      </c>
+      <c r="N28" s="210">
+        <v>1664.22</v>
+      </c>
+      <c r="O28" s="210">
+        <f>+N28*G28</f>
+        <v>28779.023615999999</v>
+      </c>
+      <c r="P28" s="210">
+        <v>1062.3599999999999</v>
+      </c>
+      <c r="Q28" s="210">
+        <v>0</v>
+      </c>
+      <c r="R28" s="210">
+        <v>1062.3599999999999</v>
+      </c>
+      <c r="S28" s="210">
+        <v>990.87</v>
+      </c>
+      <c r="T28" s="210">
+        <v>735.1</v>
+      </c>
+      <c r="U28" s="211">
+        <v>0.3785</v>
+      </c>
+      <c r="V28" s="210">
+        <v>694.02</v>
+      </c>
+      <c r="W28" s="211">
+        <v>0.2545</v>
+      </c>
+      <c r="X28" s="212">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A29" s="208">
+        <v>13429</v>
+      </c>
+      <c r="B29" s="208" t="s">
+        <v>316</v>
+      </c>
+      <c r="C29" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="209">
+        <v>46196</v>
+      </c>
+      <c r="E29" s="208" t="s">
+        <v>462</v>
+      </c>
+      <c r="F29" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="210">
+        <v>17.3477</v>
+      </c>
+      <c r="H29" s="210">
+        <v>1</v>
+      </c>
+      <c r="I29" s="210">
+        <v>38571.870000000003</v>
+      </c>
+      <c r="J29" s="210">
+        <f t="shared" ref="J29:J31" si="3">+I29*H29</f>
+        <v>38571.870000000003</v>
+      </c>
+      <c r="K29" s="210">
+        <v>4862.88</v>
+      </c>
+      <c r="L29" s="210">
+        <v>4859.21</v>
+      </c>
+      <c r="M29" s="210">
+        <v>0</v>
+      </c>
+      <c r="N29" s="210">
+        <v>24259.040000000001</v>
+      </c>
+      <c r="O29" s="210">
+        <f t="shared" si="1"/>
+        <v>24259.040000000001</v>
+      </c>
+      <c r="P29" s="210">
+        <v>14312.83</v>
+      </c>
+      <c r="Q29" s="210">
+        <v>0</v>
+      </c>
+      <c r="R29" s="210">
+        <v>14312.83</v>
+      </c>
+      <c r="S29" s="210">
+        <v>9868.35</v>
+      </c>
+      <c r="T29" s="210">
+        <v>5009.1400000000003</v>
+      </c>
+      <c r="U29" s="211">
+        <v>0.25590000000000002</v>
+      </c>
+      <c r="V29" s="210">
+        <v>5005.47</v>
+      </c>
+      <c r="W29" s="211">
+        <v>0.1298</v>
+      </c>
+      <c r="X29" s="212">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A30" s="208">
+        <v>13395</v>
+      </c>
+      <c r="B30" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" s="208" t="s">
+        <v>169</v>
+      </c>
+      <c r="D30" s="209">
+        <v>46189</v>
+      </c>
+      <c r="E30" s="208" t="s">
+        <v>463</v>
+      </c>
+      <c r="F30" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="210">
+        <v>17.187799999999999</v>
+      </c>
+      <c r="H30" s="210">
+        <v>1</v>
+      </c>
+      <c r="I30" s="210">
+        <v>2923.62</v>
+      </c>
+      <c r="J30" s="210">
+        <f t="shared" si="3"/>
+        <v>2923.62</v>
+      </c>
+      <c r="K30" s="210">
+        <v>505.82</v>
+      </c>
+      <c r="L30" s="210">
+        <v>459.88</v>
+      </c>
+      <c r="M30" s="210">
+        <v>0</v>
+      </c>
+      <c r="N30" s="210">
+        <v>1499.14</v>
+      </c>
+      <c r="O30" s="210">
+        <f t="shared" si="1"/>
+        <v>1499.14</v>
+      </c>
+      <c r="P30" s="210">
+        <v>1424.48</v>
+      </c>
+      <c r="Q30" s="210">
+        <v>0</v>
+      </c>
+      <c r="R30" s="210">
+        <v>1424.48</v>
+      </c>
+      <c r="S30" s="210">
+        <v>1424.48</v>
+      </c>
+      <c r="T30" s="210">
+        <v>964.6</v>
+      </c>
+      <c r="U30" s="211">
+        <v>0.50290000000000001</v>
+      </c>
+      <c r="V30" s="210">
+        <v>918.66</v>
+      </c>
+      <c r="W30" s="211">
+        <v>0.31419999999999998</v>
+      </c>
+      <c r="X30" s="212">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A31" s="208">
+        <v>13381</v>
+      </c>
+      <c r="B31" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="208" t="s">
+        <v>101</v>
+      </c>
+      <c r="D31" s="209">
+        <v>46178</v>
+      </c>
+      <c r="E31" s="208" t="s">
+        <v>464</v>
+      </c>
+      <c r="F31" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="210">
+        <v>17.2105</v>
+      </c>
+      <c r="H31" s="210">
+        <v>1</v>
+      </c>
+      <c r="I31" s="210">
+        <v>47016.5</v>
+      </c>
+      <c r="J31" s="210">
+        <f t="shared" si="3"/>
+        <v>47016.5</v>
+      </c>
+      <c r="K31" s="210">
+        <v>5211.1099999999997</v>
+      </c>
+      <c r="L31" s="210">
+        <v>4059.07</v>
+      </c>
+      <c r="M31" s="210">
+        <v>6063</v>
+      </c>
+      <c r="N31" s="210">
+        <v>15849.04</v>
+      </c>
+      <c r="O31" s="210">
+        <f t="shared" si="1"/>
+        <v>15849.04</v>
+      </c>
+      <c r="P31" s="210">
+        <v>8039.08</v>
+      </c>
+      <c r="Q31" s="210">
+        <v>17065.38</v>
+      </c>
+      <c r="R31" s="210">
+        <v>31167.46</v>
+      </c>
+      <c r="S31" s="210">
+        <v>25104.46</v>
+      </c>
+      <c r="T31" s="210">
+        <v>21045.39</v>
+      </c>
+      <c r="U31" s="211">
+        <v>0.5585</v>
+      </c>
+      <c r="V31" s="210">
+        <v>19893.349999999999</v>
+      </c>
+      <c r="W31" s="211">
+        <v>0.42309999999999998</v>
+      </c>
+      <c r="X31" s="212">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A32" s="208">
+        <v>13366</v>
+      </c>
+      <c r="B32" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C32" s="208" t="s">
+        <v>153</v>
+      </c>
+      <c r="D32" s="209">
+        <v>46195</v>
+      </c>
+      <c r="E32" s="208" t="s">
+        <v>465</v>
+      </c>
+      <c r="F32" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G32" s="210">
+        <v>17.253</v>
+      </c>
+      <c r="H32" s="210">
+        <v>1</v>
+      </c>
+      <c r="I32" s="210">
+        <v>108.82</v>
+      </c>
+      <c r="J32" s="210">
+        <f>+I32*G32</f>
+        <v>1877.47146</v>
+      </c>
+      <c r="K32" s="210">
+        <v>24.73</v>
+      </c>
+      <c r="L32" s="210">
+        <v>23.33</v>
+      </c>
+      <c r="M32" s="210">
+        <v>0</v>
+      </c>
+      <c r="N32" s="210">
+        <v>55.24</v>
+      </c>
+      <c r="O32" s="210">
+        <f>+N32*G32</f>
+        <v>953.05572000000006</v>
+      </c>
+      <c r="P32" s="210">
+        <v>53.58</v>
+      </c>
+      <c r="Q32" s="210">
+        <v>0</v>
+      </c>
+      <c r="R32" s="210">
+        <v>53.58</v>
+      </c>
+      <c r="S32" s="210">
+        <v>53.58</v>
+      </c>
+      <c r="T32" s="210">
+        <v>30.25</v>
+      </c>
+      <c r="U32" s="211">
+        <v>0.50519999999999998</v>
+      </c>
+      <c r="V32" s="210">
+        <v>28.85</v>
+      </c>
+      <c r="W32" s="211">
+        <v>0.2651</v>
+      </c>
+      <c r="X32" s="212">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A33" s="208">
+        <v>13342</v>
+      </c>
+      <c r="B33" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="208" t="s">
+        <v>390</v>
+      </c>
+      <c r="D33" s="209">
+        <v>46183</v>
+      </c>
+      <c r="E33" s="208" t="s">
+        <v>466</v>
+      </c>
+      <c r="F33" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="210">
+        <v>17.515699999999999</v>
+      </c>
+      <c r="H33" s="210">
+        <v>1</v>
+      </c>
+      <c r="I33" s="210">
+        <v>110053.13</v>
+      </c>
+      <c r="J33" s="210">
+        <f t="shared" ref="J33:J34" si="4">+I33*H33</f>
+        <v>110053.13</v>
+      </c>
+      <c r="K33" s="210">
+        <v>13951.56</v>
+      </c>
+      <c r="L33" s="210">
+        <v>12333.3</v>
+      </c>
+      <c r="M33" s="210">
+        <v>6367.25</v>
+      </c>
+      <c r="N33" s="210">
+        <v>49976.04</v>
+      </c>
+      <c r="O33" s="210">
+        <f t="shared" si="1"/>
+        <v>49976.04</v>
+      </c>
+      <c r="P33" s="210">
+        <v>32323.03</v>
+      </c>
+      <c r="Q33" s="210">
+        <v>21386.81</v>
+      </c>
+      <c r="R33" s="210">
+        <v>60077.09</v>
+      </c>
+      <c r="S33" s="210">
+        <v>53709.84</v>
+      </c>
+      <c r="T33" s="210">
+        <v>41376.54</v>
+      </c>
+      <c r="U33" s="211">
+        <v>0.50270000000000004</v>
+      </c>
+      <c r="V33" s="210">
+        <v>39758.28</v>
+      </c>
+      <c r="W33" s="211">
+        <v>0.36130000000000001</v>
+      </c>
+      <c r="X33" s="212">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A34" s="208">
+        <v>13336</v>
+      </c>
+      <c r="B34" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="208" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" s="209">
+        <v>46189</v>
+      </c>
+      <c r="E34" s="208" t="s">
+        <v>467</v>
+      </c>
+      <c r="F34" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="210">
+        <v>17.511800000000001</v>
+      </c>
+      <c r="H34" s="210">
+        <v>1</v>
+      </c>
+      <c r="I34" s="210">
+        <v>2144.35</v>
+      </c>
+      <c r="J34" s="210">
+        <f t="shared" si="4"/>
+        <v>2144.35</v>
+      </c>
+      <c r="K34" s="210">
+        <v>442.26</v>
+      </c>
+      <c r="L34" s="210">
+        <v>448.07</v>
+      </c>
+      <c r="M34" s="210">
+        <v>0</v>
+      </c>
+      <c r="N34" s="210">
+        <v>1523.55</v>
+      </c>
+      <c r="O34" s="210">
+        <f t="shared" si="1"/>
+        <v>1523.55</v>
+      </c>
+      <c r="P34" s="210">
+        <v>620.79999999999995</v>
+      </c>
+      <c r="Q34" s="210">
+        <v>0</v>
+      </c>
+      <c r="R34" s="210">
+        <v>620.79999999999995</v>
+      </c>
+      <c r="S34" s="210">
+        <v>619.04999999999995</v>
+      </c>
+      <c r="T34" s="210">
+        <v>170.98</v>
+      </c>
+      <c r="U34" s="211">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="V34" s="210">
+        <v>170.98</v>
+      </c>
+      <c r="W34" s="211">
+        <v>7.9699999999999993E-2</v>
+      </c>
+      <c r="X34" s="212">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A35" s="208">
+        <v>13300</v>
+      </c>
+      <c r="B35" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="208" t="s">
+        <v>153</v>
+      </c>
+      <c r="D35" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E35" s="208" t="s">
+        <v>468</v>
+      </c>
+      <c r="F35" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G35" s="210">
+        <v>17.405200000000001</v>
+      </c>
+      <c r="H35" s="210">
+        <v>1</v>
+      </c>
+      <c r="I35" s="210">
+        <v>339.2</v>
+      </c>
+      <c r="J35" s="210">
+        <f t="shared" ref="J35:J36" si="5">+I35*G35</f>
+        <v>5903.8438400000005</v>
+      </c>
+      <c r="K35" s="210">
+        <v>48.28</v>
+      </c>
+      <c r="L35" s="210">
+        <v>51.04</v>
+      </c>
+      <c r="M35" s="210">
+        <v>0</v>
+      </c>
+      <c r="N35" s="210">
+        <v>229.2</v>
+      </c>
+      <c r="O35" s="210">
+        <f t="shared" ref="O35:O36" si="6">+N35*G35</f>
+        <v>3989.2718399999999</v>
+      </c>
+      <c r="P35" s="210">
+        <v>110</v>
+      </c>
+      <c r="Q35" s="210">
+        <v>0</v>
+      </c>
+      <c r="R35" s="210">
+        <v>110</v>
+      </c>
+      <c r="S35" s="210">
+        <v>66.44</v>
+      </c>
+      <c r="T35" s="210">
+        <v>15.4</v>
+      </c>
+      <c r="U35" s="211">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="V35" s="210">
+        <v>15.4</v>
+      </c>
+      <c r="W35" s="211">
+        <v>4.5400000000000003E-2</v>
+      </c>
+      <c r="X35" s="212">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A36" s="208">
+        <v>13223</v>
+      </c>
+      <c r="B36" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="208" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="209">
+        <v>46189</v>
+      </c>
+      <c r="E36" s="208" t="s">
+        <v>268</v>
+      </c>
+      <c r="F36" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G36" s="210">
+        <v>17.415700000000001</v>
+      </c>
+      <c r="H36" s="210">
+        <v>1</v>
+      </c>
+      <c r="I36" s="210">
+        <v>2652.53</v>
+      </c>
+      <c r="J36" s="210">
+        <f t="shared" si="5"/>
+        <v>46195.666721000009</v>
+      </c>
+      <c r="K36" s="210">
+        <v>279.77</v>
+      </c>
+      <c r="L36" s="210">
+        <v>235.77</v>
+      </c>
+      <c r="M36" s="210">
+        <v>0</v>
+      </c>
+      <c r="N36" s="210">
+        <v>1382.81</v>
+      </c>
+      <c r="O36" s="210">
+        <f t="shared" si="6"/>
+        <v>24082.604116999999</v>
+      </c>
+      <c r="P36" s="210">
+        <v>1269.72</v>
+      </c>
+      <c r="Q36" s="210">
+        <v>0</v>
+      </c>
+      <c r="R36" s="210">
+        <v>1269.72</v>
+      </c>
+      <c r="S36" s="210">
+        <v>1254.8</v>
+      </c>
+      <c r="T36" s="210">
+        <v>1019.03</v>
+      </c>
+      <c r="U36" s="211">
+        <v>0.48959999999999998</v>
+      </c>
+      <c r="V36" s="210">
+        <v>975.03</v>
+      </c>
+      <c r="W36" s="211">
+        <v>0.36759999999999998</v>
+      </c>
+      <c r="X36" s="212">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A37" s="208">
+        <v>13211</v>
+      </c>
+      <c r="B37" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="208" t="s">
+        <v>261</v>
+      </c>
+      <c r="D37" s="209">
+        <v>46189</v>
+      </c>
+      <c r="E37" s="208" t="s">
+        <v>469</v>
+      </c>
+      <c r="F37" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="210">
+        <v>17.811699999999998</v>
+      </c>
+      <c r="H37" s="210">
+        <v>1</v>
+      </c>
+      <c r="I37" s="210">
+        <v>17727.2</v>
+      </c>
+      <c r="J37" s="210">
+        <f t="shared" ref="J37:J41" si="7">+I37*H37</f>
+        <v>17727.2</v>
+      </c>
+      <c r="K37" s="210">
+        <v>1896.11</v>
+      </c>
+      <c r="L37" s="210">
+        <v>1943.33</v>
+      </c>
+      <c r="M37" s="210">
+        <v>0</v>
+      </c>
+      <c r="N37" s="210">
+        <v>13025.6</v>
+      </c>
+      <c r="O37" s="210">
+        <f t="shared" si="1"/>
+        <v>13025.6</v>
+      </c>
+      <c r="P37" s="210">
+        <v>4701.6000000000004</v>
+      </c>
+      <c r="Q37" s="210">
+        <v>0</v>
+      </c>
+      <c r="R37" s="210">
+        <v>4701.6000000000004</v>
+      </c>
+      <c r="S37" s="210">
+        <v>2339.4</v>
+      </c>
+      <c r="T37" s="210">
+        <v>396.07</v>
+      </c>
+      <c r="U37" s="211">
+        <v>2.23E-2</v>
+      </c>
+      <c r="V37" s="210">
+        <v>396.07</v>
+      </c>
+      <c r="W37" s="211">
+        <v>2.23E-2</v>
+      </c>
+      <c r="X37" s="212">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A38" s="208">
+        <v>13166</v>
+      </c>
+      <c r="B38" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E38" s="208" t="s">
+        <v>470</v>
+      </c>
+      <c r="F38" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="210">
+        <v>17.777999999999999</v>
+      </c>
+      <c r="H38" s="210">
+        <v>1</v>
+      </c>
+      <c r="I38" s="210">
+        <v>225489.6</v>
+      </c>
+      <c r="J38" s="210">
+        <f t="shared" si="7"/>
+        <v>225489.6</v>
+      </c>
+      <c r="K38" s="210">
+        <v>13923.62</v>
+      </c>
+      <c r="L38" s="210">
+        <v>27766.73</v>
+      </c>
+      <c r="M38" s="210">
+        <v>0</v>
+      </c>
+      <c r="N38" s="210">
+        <v>144824.91</v>
+      </c>
+      <c r="O38" s="210">
+        <f t="shared" si="1"/>
+        <v>144824.91</v>
+      </c>
+      <c r="P38" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="Q38" s="210">
+        <v>0</v>
+      </c>
+      <c r="R38" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="S38" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="T38" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="U38" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="V38" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="W38" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="X38" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A39" s="208">
+        <v>13165</v>
+      </c>
+      <c r="B39" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D39" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E39" s="208" t="s">
+        <v>471</v>
+      </c>
+      <c r="F39" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="210">
+        <v>17.777999999999999</v>
+      </c>
+      <c r="H39" s="210">
+        <v>1</v>
+      </c>
+      <c r="I39" s="210">
+        <v>225489.6</v>
+      </c>
+      <c r="J39" s="210">
+        <f t="shared" si="7"/>
+        <v>225489.6</v>
+      </c>
+      <c r="K39" s="210">
+        <v>13923.62</v>
+      </c>
+      <c r="L39" s="210">
+        <v>27766.73</v>
+      </c>
+      <c r="M39" s="210">
+        <v>0</v>
+      </c>
+      <c r="N39" s="210">
+        <v>144824.91</v>
+      </c>
+      <c r="O39" s="210">
+        <f t="shared" si="1"/>
+        <v>144824.91</v>
+      </c>
+      <c r="P39" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="Q39" s="210">
+        <v>0</v>
+      </c>
+      <c r="R39" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="S39" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="T39" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="U39" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="V39" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="W39" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="X39" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A40" s="208">
+        <v>13164</v>
+      </c>
+      <c r="B40" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D40" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E40" s="208" t="s">
+        <v>472</v>
+      </c>
+      <c r="F40" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="210">
+        <v>17.777999999999999</v>
+      </c>
+      <c r="H40" s="210">
+        <v>1</v>
+      </c>
+      <c r="I40" s="210">
+        <v>225489.6</v>
+      </c>
+      <c r="J40" s="210">
+        <f t="shared" si="7"/>
+        <v>225489.6</v>
+      </c>
+      <c r="K40" s="210">
+        <v>13923.62</v>
+      </c>
+      <c r="L40" s="210">
+        <v>27766.73</v>
+      </c>
+      <c r="M40" s="210">
+        <v>0</v>
+      </c>
+      <c r="N40" s="210">
+        <v>144824.91</v>
+      </c>
+      <c r="O40" s="210">
+        <f t="shared" si="1"/>
+        <v>144824.91</v>
+      </c>
+      <c r="P40" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="Q40" s="210">
+        <v>0</v>
+      </c>
+      <c r="R40" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="S40" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="T40" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="U40" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="V40" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="W40" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="X40" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A41" s="208">
+        <v>13163</v>
+      </c>
+      <c r="B41" s="208" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="208" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E41" s="208" t="s">
+        <v>473</v>
+      </c>
+      <c r="F41" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G41" s="210">
+        <v>17.777999999999999</v>
+      </c>
+      <c r="H41" s="210">
+        <v>1</v>
+      </c>
+      <c r="I41" s="210">
+        <v>225489.6</v>
+      </c>
+      <c r="J41" s="210">
+        <f t="shared" si="7"/>
+        <v>225489.6</v>
+      </c>
+      <c r="K41" s="210">
+        <v>13923.62</v>
+      </c>
+      <c r="L41" s="210">
+        <v>27766.73</v>
+      </c>
+      <c r="M41" s="210">
+        <v>0</v>
+      </c>
+      <c r="N41" s="210">
+        <v>144824.91</v>
+      </c>
+      <c r="O41" s="210">
+        <f t="shared" si="1"/>
+        <v>144824.91</v>
+      </c>
+      <c r="P41" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="Q41" s="210">
+        <v>0</v>
+      </c>
+      <c r="R41" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="S41" s="210">
+        <v>80664.69</v>
+      </c>
+      <c r="T41" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="U41" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="V41" s="210">
+        <v>52897.96</v>
+      </c>
+      <c r="W41" s="211">
+        <v>0.2346</v>
+      </c>
+      <c r="X41" s="212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A42" s="208">
+        <v>12996</v>
+      </c>
+      <c r="B42" s="208" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="208" t="s">
+        <v>153</v>
+      </c>
+      <c r="D42" s="209">
+        <v>46202</v>
+      </c>
+      <c r="E42" s="208" t="s">
+        <v>474</v>
+      </c>
+      <c r="F42" s="208" t="s">
+        <v>123</v>
+      </c>
+      <c r="G42" s="210">
+        <v>17.1722</v>
+      </c>
+      <c r="H42" s="210">
+        <v>1</v>
+      </c>
+      <c r="I42" s="210">
+        <v>909.3</v>
+      </c>
+      <c r="J42" s="210">
+        <f>+I42*G42</f>
+        <v>15614.68146</v>
+      </c>
+      <c r="K42" s="210">
+        <v>98.18</v>
+      </c>
+      <c r="L42" s="210">
+        <v>71.38</v>
+      </c>
+      <c r="M42" s="210">
+        <v>0</v>
+      </c>
+      <c r="N42" s="210">
+        <v>355.15</v>
+      </c>
+      <c r="O42" s="210">
+        <f>+N42*G42</f>
+        <v>6098.7068300000001</v>
+      </c>
+      <c r="P42" s="210">
+        <v>554.15</v>
+      </c>
+      <c r="Q42" s="210">
+        <v>0</v>
+      </c>
+      <c r="R42" s="210">
+        <v>554.15</v>
+      </c>
+      <c r="S42" s="210">
+        <v>554.15</v>
+      </c>
+      <c r="T42" s="210">
+        <v>482.77</v>
+      </c>
+      <c r="U42" s="211">
+        <v>0.63890000000000002</v>
+      </c>
+      <c r="V42" s="210">
+        <v>455.97</v>
+      </c>
+      <c r="W42" s="211">
+        <v>0.50149999999999995</v>
+      </c>
+      <c r="X42" s="212">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A43" s="208">
+        <v>12965</v>
+      </c>
+      <c r="B43" s="208" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="208" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="209">
+        <v>46183</v>
+      </c>
+      <c r="E43" s="208" t="s">
+        <v>475</v>
+      </c>
+      <c r="F43" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G43" s="210">
+        <v>17.1798</v>
+      </c>
+      <c r="H43" s="210">
+        <v>1</v>
+      </c>
+      <c r="I43" s="210">
+        <v>258254.87</v>
+      </c>
+      <c r="J43" s="210">
+        <f t="shared" ref="J43:J44" si="8">+I43*H43</f>
+        <v>258254.87</v>
+      </c>
+      <c r="K43" s="210">
+        <v>26662.080000000002</v>
+      </c>
+      <c r="L43" s="210">
+        <v>29143.63</v>
+      </c>
+      <c r="M43" s="210">
+        <v>31146.55</v>
+      </c>
+      <c r="N43" s="210">
+        <v>139705.29</v>
+      </c>
+      <c r="O43" s="210">
+        <f t="shared" si="1"/>
+        <v>139705.29</v>
+      </c>
+      <c r="P43" s="210">
+        <v>52588.44</v>
+      </c>
+      <c r="Q43" s="210">
+        <v>34814.589999999997</v>
+      </c>
+      <c r="R43" s="210">
+        <v>118549.58</v>
+      </c>
+      <c r="S43" s="210">
+        <v>87403.03</v>
+      </c>
+      <c r="T43" s="210">
+        <v>58259.4</v>
+      </c>
+      <c r="U43" s="211">
+        <v>0.22559999999999999</v>
+      </c>
+      <c r="V43" s="210">
+        <v>58259.4</v>
+      </c>
+      <c r="W43" s="211">
+        <v>0.22559999999999999</v>
+      </c>
+      <c r="X43" s="212">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A44" s="208">
+        <v>12105</v>
+      </c>
+      <c r="B44" s="208" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="208" t="s">
+        <v>67</v>
+      </c>
+      <c r="D44" s="209">
+        <v>46203</v>
+      </c>
+      <c r="E44" s="208" t="s">
+        <v>476</v>
+      </c>
+      <c r="F44" s="208" t="s">
+        <v>21</v>
+      </c>
+      <c r="G44" s="210">
+        <v>18.556999999999999</v>
+      </c>
+      <c r="H44" s="210">
+        <v>1</v>
+      </c>
+      <c r="I44" s="210">
+        <v>2022597.26</v>
+      </c>
+      <c r="J44" s="210">
+        <f t="shared" si="8"/>
+        <v>2022597.26</v>
+      </c>
+      <c r="K44" s="210">
+        <v>199907.13</v>
+      </c>
+      <c r="L44" s="210">
+        <v>173061.71</v>
+      </c>
+      <c r="M44" s="210">
+        <v>239879.53</v>
+      </c>
+      <c r="N44" s="210">
+        <v>860641.44</v>
+      </c>
+      <c r="O44" s="210">
+        <f t="shared" si="1"/>
+        <v>860641.44</v>
+      </c>
+      <c r="P44" s="210">
+        <v>817989.34</v>
+      </c>
+      <c r="Q44" s="210">
+        <v>104086.95</v>
+      </c>
+      <c r="R44" s="210">
+        <v>1161955.82</v>
+      </c>
+      <c r="S44" s="210">
+        <v>921001.6</v>
+      </c>
+      <c r="T44" s="210">
+        <v>747939.89</v>
+      </c>
+      <c r="U44" s="211">
+        <v>0.46860000000000002</v>
+      </c>
+      <c r="V44" s="210">
+        <v>721094.47</v>
+      </c>
+      <c r="W44" s="211">
+        <v>0.35649999999999998</v>
+      </c>
+      <c r="X44" s="212">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="I45" s="206">
+        <f>SUBTOTAL(9,I2:I44)</f>
+        <v>3943726.2199999997</v>
+      </c>
+      <c r="J45" s="214">
+        <f>SUBTOTAL(9,J2:J44)</f>
+        <v>4097433.4141200008</v>
+      </c>
+      <c r="O45" s="207">
+        <f>SUM(O2:O44)</f>
+        <v>2023683.6897479999</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:X44" xr:uid="{3EFAB7BA-C287-458D-80E8-9131283220CB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>